--- a/src/accounting/jurnal-dagang-umum-penutup/materi penutup.xlsx
+++ b/src/accounting/jurnal-dagang-umum-penutup/materi penutup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software-Developer-JS\project-accounting-electron\src\accounting\jurnal-dagang-umum-penutup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software-Developer-JS\electron-sqlite3\src\accounting\jurnal-dagang-umum-penutup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD1A238-57F0-4BA5-94F7-039A9F7D8EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C582966D-6682-42A1-995D-75AAA315AD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="748" firstSheet="12" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="748" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tips - Posisi Akun - Siklus" sheetId="1" r:id="rId1"/>
@@ -2137,6 +2137,11 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2145,24 +2150,19 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3941,60 +3941,60 @@
       </c>
     </row>
     <row r="3" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="162" t="s">
+      <c r="A3" s="165" t="s">
         <v>191</v>
       </c>
-      <c r="B3" s="162" t="s">
+      <c r="B3" s="165" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="162" t="s">
+      <c r="C3" s="165" t="s">
         <v>192</v>
       </c>
-      <c r="D3" s="165" t="s">
+      <c r="D3" s="168" t="s">
         <v>284</v>
       </c>
       <c r="E3" s="159"/>
       <c r="F3" s="160"/>
-      <c r="G3" s="165" t="s">
+      <c r="G3" s="168" t="s">
         <v>285</v>
       </c>
       <c r="H3" s="159"/>
       <c r="I3" s="160"/>
-      <c r="J3" s="165" t="s">
+      <c r="J3" s="168" t="s">
         <v>286</v>
       </c>
       <c r="K3" s="159"/>
       <c r="L3" s="160"/>
       <c r="P3" s="18"/>
-      <c r="V3" s="162" t="s">
+      <c r="V3" s="165" t="s">
         <v>191</v>
       </c>
-      <c r="W3" s="162" t="s">
+      <c r="W3" s="165" t="s">
         <v>229</v>
       </c>
-      <c r="X3" s="162" t="s">
+      <c r="X3" s="165" t="s">
         <v>192</v>
       </c>
-      <c r="Y3" s="165" t="s">
+      <c r="Y3" s="168" t="s">
         <v>284</v>
       </c>
       <c r="Z3" s="159"/>
       <c r="AA3" s="160"/>
-      <c r="AB3" s="165" t="s">
+      <c r="AB3" s="168" t="s">
         <v>285</v>
       </c>
       <c r="AC3" s="159"/>
       <c r="AD3" s="160"/>
-      <c r="AE3" s="165" t="s">
+      <c r="AE3" s="168" t="s">
         <v>286</v>
       </c>
       <c r="AF3" s="159"/>
       <c r="AG3" s="160"/>
     </row>
     <row r="4" spans="1:33" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="164"/>
-      <c r="B4" s="164"/>
-      <c r="C4" s="164"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="167"/>
+      <c r="C4" s="167"/>
       <c r="D4" s="26" t="s">
         <v>270</v>
       </c>
@@ -4023,9 +4023,9 @@
         <v>188</v>
       </c>
       <c r="P4" s="18"/>
-      <c r="V4" s="164"/>
-      <c r="W4" s="164"/>
-      <c r="X4" s="164"/>
+      <c r="V4" s="167"/>
+      <c r="W4" s="167"/>
+      <c r="X4" s="167"/>
       <c r="Y4" s="26" t="s">
         <v>270</v>
       </c>
@@ -8244,70 +8244,70 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="172" t="s">
+      <c r="A2" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="172" t="s">
+      <c r="C2" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="172" t="s">
+      <c r="D2" s="173" t="s">
         <v>264</v>
       </c>
-      <c r="E2" s="172" t="s">
+      <c r="E2" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="172" t="s">
+      <c r="F2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="173" t="s">
+      <c r="G2" s="174" t="s">
         <v>299</v>
       </c>
-      <c r="K2" s="172" t="s">
+      <c r="K2" s="173" t="s">
         <v>215</v>
       </c>
-      <c r="L2" s="172" t="s">
+      <c r="L2" s="173" t="s">
         <v>267</v>
       </c>
-      <c r="M2" s="172" t="s">
+      <c r="M2" s="173" t="s">
         <v>53</v>
       </c>
-      <c r="N2" s="172" t="s">
+      <c r="N2" s="173" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="172" t="s">
+      <c r="O2" s="173" t="s">
         <v>84</v>
       </c>
-      <c r="P2" s="174" t="s">
+      <c r="P2" s="172" t="s">
         <v>268</v>
       </c>
       <c r="Q2" s="160"/>
-      <c r="R2" s="172" t="s">
+      <c r="R2" s="173" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="164"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="164"/>
-      <c r="K3" s="164"/>
-      <c r="L3" s="164"/>
-      <c r="M3" s="164"/>
-      <c r="N3" s="164"/>
-      <c r="O3" s="164"/>
+      <c r="A3" s="167"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="167"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="167"/>
+      <c r="K3" s="167"/>
+      <c r="L3" s="167"/>
+      <c r="M3" s="167"/>
+      <c r="N3" s="167"/>
+      <c r="O3" s="167"/>
       <c r="P3" s="81" t="s">
         <v>6</v>
       </c>
       <c r="Q3" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="R3" s="164"/>
+      <c r="R3" s="167"/>
     </row>
     <row r="4" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
@@ -8556,36 +8556,36 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="172" t="s">
+      <c r="A19" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B19" s="172" t="s">
+      <c r="B19" s="173" t="s">
         <v>192</v>
       </c>
-      <c r="C19" s="172" t="s">
+      <c r="C19" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="D19" s="172" t="s">
+      <c r="D19" s="173" t="s">
         <v>264</v>
       </c>
-      <c r="E19" s="172" t="s">
+      <c r="E19" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="172" t="s">
+      <c r="F19" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="G19" s="173" t="s">
+      <c r="G19" s="174" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="164"/>
-      <c r="B20" s="164"/>
-      <c r="C20" s="164"/>
-      <c r="D20" s="164"/>
-      <c r="E20" s="164"/>
-      <c r="F20" s="164"/>
-      <c r="G20" s="164"/>
+      <c r="A20" s="167"/>
+      <c r="B20" s="167"/>
+      <c r="C20" s="167"/>
+      <c r="D20" s="167"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="167"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="82" t="s">
@@ -8729,34 +8729,34 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="172" t="s">
+      <c r="A36" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B36" s="172" t="s">
+      <c r="B36" s="173" t="s">
         <v>192</v>
       </c>
-      <c r="C36" s="172" t="s">
+      <c r="C36" s="173" t="s">
         <v>229</v>
       </c>
       <c r="D36" s="78"/>
-      <c r="E36" s="172" t="s">
+      <c r="E36" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="F36" s="172" t="s">
+      <c r="F36" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="G36" s="173" t="s">
+      <c r="G36" s="174" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="164"/>
-      <c r="B37" s="164"/>
-      <c r="C37" s="164"/>
+      <c r="A37" s="167"/>
+      <c r="B37" s="167"/>
+      <c r="C37" s="167"/>
       <c r="D37" s="115"/>
-      <c r="E37" s="164"/>
-      <c r="F37" s="164"/>
-      <c r="G37" s="164"/>
+      <c r="E37" s="167"/>
+      <c r="F37" s="167"/>
+      <c r="G37" s="167"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="33"/>
@@ -9827,6 +9827,19 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="A2:A3"/>
@@ -9841,19 +9854,6 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -9915,52 +9915,52 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="172" t="s">
+      <c r="A5" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B5" s="172" t="s">
+      <c r="B5" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C5" s="172" t="s">
+      <c r="C5" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D5" s="172" t="s">
+      <c r="D5" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E5" s="172" t="s">
+      <c r="E5" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F5" s="174" t="s">
+      <c r="F5" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G5" s="160"/>
       <c r="H5" s="116"/>
-      <c r="J5" s="172" t="s">
+      <c r="J5" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K5" s="172" t="s">
+      <c r="K5" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L5" s="172" t="s">
+      <c r="L5" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M5" s="172" t="s">
+      <c r="M5" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N5" s="172" t="s">
+      <c r="N5" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O5" s="174" t="s">
+      <c r="O5" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P5" s="160"/>
     </row>
     <row r="6" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="164"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
+      <c r="A6" s="167"/>
+      <c r="B6" s="167"/>
+      <c r="C6" s="167"/>
+      <c r="D6" s="167"/>
+      <c r="E6" s="167"/>
       <c r="F6" s="117" t="s">
         <v>314</v>
       </c>
@@ -9968,11 +9968,11 @@
         <v>315</v>
       </c>
       <c r="H6" s="116"/>
-      <c r="J6" s="164"/>
-      <c r="K6" s="164"/>
-      <c r="L6" s="164"/>
-      <c r="M6" s="164"/>
-      <c r="N6" s="164"/>
+      <c r="J6" s="167"/>
+      <c r="K6" s="167"/>
+      <c r="L6" s="167"/>
+      <c r="M6" s="167"/>
+      <c r="N6" s="167"/>
       <c r="O6" s="117" t="s">
         <v>314</v>
       </c>
@@ -10265,52 +10265,52 @@
       </c>
     </row>
     <row r="19" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="172" t="s">
+      <c r="A19" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B19" s="172" t="s">
+      <c r="B19" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C19" s="172" t="s">
+      <c r="C19" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D19" s="172" t="s">
+      <c r="D19" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E19" s="172" t="s">
+      <c r="E19" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F19" s="174" t="s">
+      <c r="F19" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G19" s="160"/>
       <c r="H19" s="116"/>
-      <c r="J19" s="172" t="s">
+      <c r="J19" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K19" s="172" t="s">
+      <c r="K19" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L19" s="172" t="s">
+      <c r="L19" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M19" s="172" t="s">
+      <c r="M19" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N19" s="172" t="s">
+      <c r="N19" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O19" s="174" t="s">
+      <c r="O19" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P19" s="160"/>
     </row>
     <row r="20" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="164"/>
-      <c r="B20" s="164"/>
-      <c r="C20" s="164"/>
-      <c r="D20" s="164"/>
-      <c r="E20" s="164"/>
+      <c r="A20" s="167"/>
+      <c r="B20" s="167"/>
+      <c r="C20" s="167"/>
+      <c r="D20" s="167"/>
+      <c r="E20" s="167"/>
       <c r="F20" s="117" t="s">
         <v>314</v>
       </c>
@@ -10318,11 +10318,11 @@
         <v>315</v>
       </c>
       <c r="H20" s="116"/>
-      <c r="J20" s="164"/>
-      <c r="K20" s="164"/>
-      <c r="L20" s="164"/>
-      <c r="M20" s="164"/>
-      <c r="N20" s="164"/>
+      <c r="J20" s="167"/>
+      <c r="K20" s="167"/>
+      <c r="L20" s="167"/>
+      <c r="M20" s="167"/>
+      <c r="N20" s="167"/>
       <c r="O20" s="117" t="s">
         <v>314</v>
       </c>
@@ -10515,52 +10515,52 @@
       </c>
     </row>
     <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="172" t="s">
+      <c r="A29" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B29" s="172" t="s">
+      <c r="B29" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C29" s="172" t="s">
+      <c r="C29" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D29" s="172" t="s">
+      <c r="D29" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E29" s="172" t="s">
+      <c r="E29" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F29" s="174" t="s">
+      <c r="F29" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G29" s="160"/>
       <c r="H29" s="116"/>
-      <c r="J29" s="172" t="s">
+      <c r="J29" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K29" s="172" t="s">
+      <c r="K29" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L29" s="172" t="s">
+      <c r="L29" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M29" s="172" t="s">
+      <c r="M29" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N29" s="172" t="s">
+      <c r="N29" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O29" s="174" t="s">
+      <c r="O29" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P29" s="160"/>
     </row>
     <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="164"/>
-      <c r="B30" s="164"/>
-      <c r="C30" s="164"/>
-      <c r="D30" s="164"/>
-      <c r="E30" s="164"/>
+      <c r="A30" s="167"/>
+      <c r="B30" s="167"/>
+      <c r="C30" s="167"/>
+      <c r="D30" s="167"/>
+      <c r="E30" s="167"/>
       <c r="F30" s="117" t="s">
         <v>314</v>
       </c>
@@ -10568,11 +10568,11 @@
         <v>315</v>
       </c>
       <c r="H30" s="116"/>
-      <c r="J30" s="164"/>
-      <c r="K30" s="164"/>
-      <c r="L30" s="164"/>
-      <c r="M30" s="164"/>
-      <c r="N30" s="164"/>
+      <c r="J30" s="167"/>
+      <c r="K30" s="167"/>
+      <c r="L30" s="167"/>
+      <c r="M30" s="167"/>
+      <c r="N30" s="167"/>
       <c r="O30" s="117" t="s">
         <v>314</v>
       </c>
@@ -10651,52 +10651,52 @@
       </c>
     </row>
     <row r="35" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="172" t="s">
+      <c r="A35" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B35" s="172" t="s">
+      <c r="B35" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C35" s="172" t="s">
+      <c r="C35" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D35" s="172" t="s">
+      <c r="D35" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E35" s="172" t="s">
+      <c r="E35" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F35" s="174" t="s">
+      <c r="F35" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G35" s="160"/>
       <c r="H35" s="116"/>
-      <c r="J35" s="172" t="s">
+      <c r="J35" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K35" s="172" t="s">
+      <c r="K35" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L35" s="172" t="s">
+      <c r="L35" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M35" s="172" t="s">
+      <c r="M35" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N35" s="172" t="s">
+      <c r="N35" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O35" s="174" t="s">
+      <c r="O35" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P35" s="160"/>
     </row>
     <row r="36" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="164"/>
-      <c r="B36" s="164"/>
-      <c r="C36" s="164"/>
-      <c r="D36" s="164"/>
-      <c r="E36" s="164"/>
+      <c r="A36" s="167"/>
+      <c r="B36" s="167"/>
+      <c r="C36" s="167"/>
+      <c r="D36" s="167"/>
+      <c r="E36" s="167"/>
       <c r="F36" s="117" t="s">
         <v>314</v>
       </c>
@@ -10704,11 +10704,11 @@
         <v>315</v>
       </c>
       <c r="H36" s="116"/>
-      <c r="J36" s="164"/>
-      <c r="K36" s="164"/>
-      <c r="L36" s="164"/>
-      <c r="M36" s="164"/>
-      <c r="N36" s="164"/>
+      <c r="J36" s="167"/>
+      <c r="K36" s="167"/>
+      <c r="L36" s="167"/>
+      <c r="M36" s="167"/>
+      <c r="N36" s="167"/>
       <c r="O36" s="117" t="s">
         <v>314</v>
       </c>
@@ -10787,52 +10787,52 @@
       </c>
     </row>
     <row r="41" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="172" t="s">
+      <c r="A41" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B41" s="172" t="s">
+      <c r="B41" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C41" s="172" t="s">
+      <c r="C41" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D41" s="172" t="s">
+      <c r="D41" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E41" s="172" t="s">
+      <c r="E41" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F41" s="174" t="s">
+      <c r="F41" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G41" s="160"/>
       <c r="H41" s="116"/>
-      <c r="J41" s="172" t="s">
+      <c r="J41" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K41" s="172" t="s">
+      <c r="K41" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L41" s="172" t="s">
+      <c r="L41" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M41" s="172" t="s">
+      <c r="M41" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N41" s="172" t="s">
+      <c r="N41" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O41" s="174" t="s">
+      <c r="O41" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P41" s="160"/>
     </row>
     <row r="42" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="164"/>
-      <c r="B42" s="164"/>
-      <c r="C42" s="164"/>
-      <c r="D42" s="164"/>
-      <c r="E42" s="164"/>
+      <c r="A42" s="167"/>
+      <c r="B42" s="167"/>
+      <c r="C42" s="167"/>
+      <c r="D42" s="167"/>
+      <c r="E42" s="167"/>
       <c r="F42" s="117" t="s">
         <v>314</v>
       </c>
@@ -10840,11 +10840,11 @@
         <v>315</v>
       </c>
       <c r="H42" s="116"/>
-      <c r="J42" s="164"/>
-      <c r="K42" s="164"/>
-      <c r="L42" s="164"/>
-      <c r="M42" s="164"/>
-      <c r="N42" s="164"/>
+      <c r="J42" s="167"/>
+      <c r="K42" s="167"/>
+      <c r="L42" s="167"/>
+      <c r="M42" s="167"/>
+      <c r="N42" s="167"/>
       <c r="O42" s="117" t="s">
         <v>314</v>
       </c>
@@ -10923,52 +10923,52 @@
       </c>
     </row>
     <row r="47" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="172" t="s">
+      <c r="A47" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B47" s="172" t="s">
+      <c r="B47" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C47" s="172" t="s">
+      <c r="C47" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D47" s="172" t="s">
+      <c r="D47" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E47" s="172" t="s">
+      <c r="E47" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F47" s="174" t="s">
+      <c r="F47" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G47" s="160"/>
       <c r="H47" s="116"/>
-      <c r="J47" s="172" t="s">
+      <c r="J47" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K47" s="172" t="s">
+      <c r="K47" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L47" s="172" t="s">
+      <c r="L47" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M47" s="172" t="s">
+      <c r="M47" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N47" s="172" t="s">
+      <c r="N47" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O47" s="174" t="s">
+      <c r="O47" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P47" s="160"/>
     </row>
     <row r="48" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="164"/>
-      <c r="B48" s="164"/>
-      <c r="C48" s="164"/>
-      <c r="D48" s="164"/>
-      <c r="E48" s="164"/>
+      <c r="A48" s="167"/>
+      <c r="B48" s="167"/>
+      <c r="C48" s="167"/>
+      <c r="D48" s="167"/>
+      <c r="E48" s="167"/>
       <c r="F48" s="117" t="s">
         <v>314</v>
       </c>
@@ -10976,11 +10976,11 @@
         <v>315</v>
       </c>
       <c r="H48" s="116"/>
-      <c r="J48" s="164"/>
-      <c r="K48" s="164"/>
-      <c r="L48" s="164"/>
-      <c r="M48" s="164"/>
-      <c r="N48" s="164"/>
+      <c r="J48" s="167"/>
+      <c r="K48" s="167"/>
+      <c r="L48" s="167"/>
+      <c r="M48" s="167"/>
+      <c r="N48" s="167"/>
       <c r="O48" s="117" t="s">
         <v>314</v>
       </c>
@@ -11061,52 +11061,52 @@
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="172" t="s">
+      <c r="A53" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B53" s="172" t="s">
+      <c r="B53" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C53" s="172" t="s">
+      <c r="C53" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D53" s="172" t="s">
+      <c r="D53" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E53" s="172" t="s">
+      <c r="E53" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F53" s="174" t="s">
+      <c r="F53" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G53" s="160"/>
       <c r="H53" s="116"/>
-      <c r="J53" s="172" t="s">
+      <c r="J53" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K53" s="172" t="s">
+      <c r="K53" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L53" s="172" t="s">
+      <c r="L53" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M53" s="172" t="s">
+      <c r="M53" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N53" s="172" t="s">
+      <c r="N53" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O53" s="174" t="s">
+      <c r="O53" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P53" s="160"/>
     </row>
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="164"/>
-      <c r="B54" s="164"/>
-      <c r="C54" s="164"/>
-      <c r="D54" s="164"/>
-      <c r="E54" s="164"/>
+      <c r="A54" s="167"/>
+      <c r="B54" s="167"/>
+      <c r="C54" s="167"/>
+      <c r="D54" s="167"/>
+      <c r="E54" s="167"/>
       <c r="F54" s="117" t="s">
         <v>314</v>
       </c>
@@ -11114,11 +11114,11 @@
         <v>315</v>
       </c>
       <c r="H54" s="116"/>
-      <c r="J54" s="164"/>
-      <c r="K54" s="164"/>
-      <c r="L54" s="164"/>
-      <c r="M54" s="164"/>
-      <c r="N54" s="164"/>
+      <c r="J54" s="167"/>
+      <c r="K54" s="167"/>
+      <c r="L54" s="167"/>
+      <c r="M54" s="167"/>
+      <c r="N54" s="167"/>
       <c r="O54" s="117" t="s">
         <v>314</v>
       </c>
@@ -11199,52 +11199,52 @@
       </c>
     </row>
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="172" t="s">
+      <c r="A59" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B59" s="172" t="s">
+      <c r="B59" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C59" s="172" t="s">
+      <c r="C59" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D59" s="172" t="s">
+      <c r="D59" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E59" s="172" t="s">
+      <c r="E59" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F59" s="174" t="s">
+      <c r="F59" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G59" s="160"/>
       <c r="H59" s="116"/>
-      <c r="J59" s="172" t="s">
+      <c r="J59" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K59" s="172" t="s">
+      <c r="K59" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L59" s="172" t="s">
+      <c r="L59" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M59" s="172" t="s">
+      <c r="M59" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N59" s="172" t="s">
+      <c r="N59" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O59" s="174" t="s">
+      <c r="O59" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P59" s="160"/>
     </row>
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="164"/>
-      <c r="B60" s="164"/>
-      <c r="C60" s="164"/>
-      <c r="D60" s="164"/>
-      <c r="E60" s="164"/>
+      <c r="A60" s="167"/>
+      <c r="B60" s="167"/>
+      <c r="C60" s="167"/>
+      <c r="D60" s="167"/>
+      <c r="E60" s="167"/>
       <c r="F60" s="117" t="s">
         <v>314</v>
       </c>
@@ -11252,11 +11252,11 @@
         <v>315</v>
       </c>
       <c r="H60" s="116"/>
-      <c r="J60" s="164"/>
-      <c r="K60" s="164"/>
-      <c r="L60" s="164"/>
-      <c r="M60" s="164"/>
-      <c r="N60" s="164"/>
+      <c r="J60" s="167"/>
+      <c r="K60" s="167"/>
+      <c r="L60" s="167"/>
+      <c r="M60" s="167"/>
+      <c r="N60" s="167"/>
       <c r="O60" s="117" t="s">
         <v>314</v>
       </c>
@@ -11455,52 +11455,52 @@
       </c>
     </row>
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="172" t="s">
+      <c r="A69" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B69" s="172" t="s">
+      <c r="B69" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C69" s="172" t="s">
+      <c r="C69" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D69" s="172" t="s">
+      <c r="D69" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E69" s="172" t="s">
+      <c r="E69" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F69" s="174" t="s">
+      <c r="F69" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G69" s="160"/>
       <c r="H69" s="116"/>
-      <c r="J69" s="172" t="s">
+      <c r="J69" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K69" s="172" t="s">
+      <c r="K69" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L69" s="172" t="s">
+      <c r="L69" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M69" s="172" t="s">
+      <c r="M69" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N69" s="172" t="s">
+      <c r="N69" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O69" s="174" t="s">
+      <c r="O69" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P69" s="160"/>
     </row>
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="164"/>
-      <c r="B70" s="164"/>
-      <c r="C70" s="164"/>
-      <c r="D70" s="164"/>
-      <c r="E70" s="164"/>
+      <c r="A70" s="167"/>
+      <c r="B70" s="167"/>
+      <c r="C70" s="167"/>
+      <c r="D70" s="167"/>
+      <c r="E70" s="167"/>
       <c r="F70" s="117" t="s">
         <v>314</v>
       </c>
@@ -11508,11 +11508,11 @@
         <v>315</v>
       </c>
       <c r="H70" s="116"/>
-      <c r="J70" s="164"/>
-      <c r="K70" s="164"/>
-      <c r="L70" s="164"/>
-      <c r="M70" s="164"/>
-      <c r="N70" s="164"/>
+      <c r="J70" s="167"/>
+      <c r="K70" s="167"/>
+      <c r="L70" s="167"/>
+      <c r="M70" s="167"/>
+      <c r="N70" s="167"/>
       <c r="O70" s="117" t="s">
         <v>314</v>
       </c>
@@ -11591,52 +11591,52 @@
       </c>
     </row>
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="172" t="s">
+      <c r="A75" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B75" s="172" t="s">
+      <c r="B75" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C75" s="172" t="s">
+      <c r="C75" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D75" s="172" t="s">
+      <c r="D75" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E75" s="172" t="s">
+      <c r="E75" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F75" s="174" t="s">
+      <c r="F75" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G75" s="160"/>
       <c r="H75" s="116"/>
-      <c r="J75" s="172" t="s">
+      <c r="J75" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K75" s="172" t="s">
+      <c r="K75" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L75" s="172" t="s">
+      <c r="L75" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M75" s="172" t="s">
+      <c r="M75" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N75" s="172" t="s">
+      <c r="N75" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O75" s="174" t="s">
+      <c r="O75" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P75" s="160"/>
     </row>
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="164"/>
-      <c r="B76" s="164"/>
-      <c r="C76" s="164"/>
-      <c r="D76" s="164"/>
-      <c r="E76" s="164"/>
+      <c r="A76" s="167"/>
+      <c r="B76" s="167"/>
+      <c r="C76" s="167"/>
+      <c r="D76" s="167"/>
+      <c r="E76" s="167"/>
       <c r="F76" s="117" t="s">
         <v>314</v>
       </c>
@@ -11644,11 +11644,11 @@
         <v>315</v>
       </c>
       <c r="H76" s="116"/>
-      <c r="J76" s="164"/>
-      <c r="K76" s="164"/>
-      <c r="L76" s="164"/>
-      <c r="M76" s="164"/>
-      <c r="N76" s="164"/>
+      <c r="J76" s="167"/>
+      <c r="K76" s="167"/>
+      <c r="L76" s="167"/>
+      <c r="M76" s="167"/>
+      <c r="N76" s="167"/>
       <c r="O76" s="117" t="s">
         <v>314</v>
       </c>
@@ -11727,52 +11727,52 @@
       </c>
     </row>
     <row r="81" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="172" t="s">
+      <c r="A81" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B81" s="172" t="s">
+      <c r="B81" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C81" s="172" t="s">
+      <c r="C81" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D81" s="172" t="s">
+      <c r="D81" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E81" s="172" t="s">
+      <c r="E81" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F81" s="174" t="s">
+      <c r="F81" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G81" s="160"/>
       <c r="H81" s="116"/>
-      <c r="J81" s="172" t="s">
+      <c r="J81" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K81" s="172" t="s">
+      <c r="K81" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L81" s="172" t="s">
+      <c r="L81" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M81" s="172" t="s">
+      <c r="M81" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N81" s="172" t="s">
+      <c r="N81" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O81" s="174" t="s">
+      <c r="O81" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P81" s="160"/>
     </row>
     <row r="82" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="164"/>
-      <c r="B82" s="164"/>
-      <c r="C82" s="164"/>
-      <c r="D82" s="164"/>
-      <c r="E82" s="164"/>
+      <c r="A82" s="167"/>
+      <c r="B82" s="167"/>
+      <c r="C82" s="167"/>
+      <c r="D82" s="167"/>
+      <c r="E82" s="167"/>
       <c r="F82" s="117" t="s">
         <v>314</v>
       </c>
@@ -11780,11 +11780,11 @@
         <v>315</v>
       </c>
       <c r="H82" s="116"/>
-      <c r="J82" s="164"/>
-      <c r="K82" s="164"/>
-      <c r="L82" s="164"/>
-      <c r="M82" s="164"/>
-      <c r="N82" s="164"/>
+      <c r="J82" s="167"/>
+      <c r="K82" s="167"/>
+      <c r="L82" s="167"/>
+      <c r="M82" s="167"/>
+      <c r="N82" s="167"/>
       <c r="O82" s="117" t="s">
         <v>314</v>
       </c>
@@ -11946,52 +11946,52 @@
       </c>
     </row>
     <row r="90" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="172" t="s">
+      <c r="A90" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B90" s="172" t="s">
+      <c r="B90" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C90" s="172" t="s">
+      <c r="C90" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D90" s="172" t="s">
+      <c r="D90" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E90" s="172" t="s">
+      <c r="E90" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F90" s="174" t="s">
+      <c r="F90" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G90" s="160"/>
       <c r="H90" s="116"/>
-      <c r="J90" s="172" t="s">
+      <c r="J90" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K90" s="172" t="s">
+      <c r="K90" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L90" s="172" t="s">
+      <c r="L90" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M90" s="172" t="s">
+      <c r="M90" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N90" s="172" t="s">
+      <c r="N90" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O90" s="174" t="s">
+      <c r="O90" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P90" s="160"/>
     </row>
     <row r="91" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="164"/>
-      <c r="B91" s="164"/>
-      <c r="C91" s="164"/>
-      <c r="D91" s="164"/>
-      <c r="E91" s="164"/>
+      <c r="A91" s="167"/>
+      <c r="B91" s="167"/>
+      <c r="C91" s="167"/>
+      <c r="D91" s="167"/>
+      <c r="E91" s="167"/>
       <c r="F91" s="117" t="s">
         <v>314</v>
       </c>
@@ -11999,11 +11999,11 @@
         <v>315</v>
       </c>
       <c r="H91" s="116"/>
-      <c r="J91" s="164"/>
-      <c r="K91" s="164"/>
-      <c r="L91" s="164"/>
-      <c r="M91" s="164"/>
-      <c r="N91" s="164"/>
+      <c r="J91" s="167"/>
+      <c r="K91" s="167"/>
+      <c r="L91" s="167"/>
+      <c r="M91" s="167"/>
+      <c r="N91" s="167"/>
       <c r="O91" s="117" t="s">
         <v>314</v>
       </c>
@@ -12082,52 +12082,52 @@
       </c>
     </row>
     <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="172" t="s">
+      <c r="A96" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B96" s="172" t="s">
+      <c r="B96" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C96" s="172" t="s">
+      <c r="C96" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D96" s="172" t="s">
+      <c r="D96" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E96" s="172" t="s">
+      <c r="E96" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F96" s="174" t="s">
+      <c r="F96" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G96" s="160"/>
       <c r="H96" s="116"/>
-      <c r="J96" s="172" t="s">
+      <c r="J96" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K96" s="172" t="s">
+      <c r="K96" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L96" s="172" t="s">
+      <c r="L96" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M96" s="172" t="s">
+      <c r="M96" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N96" s="172" t="s">
+      <c r="N96" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O96" s="174" t="s">
+      <c r="O96" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P96" s="160"/>
     </row>
     <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="164"/>
-      <c r="B97" s="164"/>
-      <c r="C97" s="164"/>
-      <c r="D97" s="164"/>
-      <c r="E97" s="164"/>
+      <c r="A97" s="167"/>
+      <c r="B97" s="167"/>
+      <c r="C97" s="167"/>
+      <c r="D97" s="167"/>
+      <c r="E97" s="167"/>
       <c r="F97" s="117" t="s">
         <v>314</v>
       </c>
@@ -12135,11 +12135,11 @@
         <v>315</v>
       </c>
       <c r="H97" s="116"/>
-      <c r="J97" s="164"/>
-      <c r="K97" s="164"/>
-      <c r="L97" s="164"/>
-      <c r="M97" s="164"/>
-      <c r="N97" s="164"/>
+      <c r="J97" s="167"/>
+      <c r="K97" s="167"/>
+      <c r="L97" s="167"/>
+      <c r="M97" s="167"/>
+      <c r="N97" s="167"/>
       <c r="O97" s="117" t="s">
         <v>314</v>
       </c>
@@ -12301,52 +12301,52 @@
       </c>
     </row>
     <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="172" t="s">
+      <c r="A105" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B105" s="172" t="s">
+      <c r="B105" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C105" s="172" t="s">
+      <c r="C105" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D105" s="172" t="s">
+      <c r="D105" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E105" s="172" t="s">
+      <c r="E105" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F105" s="174" t="s">
+      <c r="F105" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G105" s="160"/>
       <c r="H105" s="116"/>
-      <c r="J105" s="172" t="s">
+      <c r="J105" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K105" s="172" t="s">
+      <c r="K105" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L105" s="172" t="s">
+      <c r="L105" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M105" s="172" t="s">
+      <c r="M105" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N105" s="172" t="s">
+      <c r="N105" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O105" s="174" t="s">
+      <c r="O105" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P105" s="160"/>
     </row>
     <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="164"/>
-      <c r="B106" s="164"/>
-      <c r="C106" s="164"/>
-      <c r="D106" s="164"/>
-      <c r="E106" s="164"/>
+      <c r="A106" s="167"/>
+      <c r="B106" s="167"/>
+      <c r="C106" s="167"/>
+      <c r="D106" s="167"/>
+      <c r="E106" s="167"/>
       <c r="F106" s="117" t="s">
         <v>314</v>
       </c>
@@ -12354,11 +12354,11 @@
         <v>315</v>
       </c>
       <c r="H106" s="116"/>
-      <c r="J106" s="164"/>
-      <c r="K106" s="164"/>
-      <c r="L106" s="164"/>
-      <c r="M106" s="164"/>
-      <c r="N106" s="164"/>
+      <c r="J106" s="167"/>
+      <c r="K106" s="167"/>
+      <c r="L106" s="167"/>
+      <c r="M106" s="167"/>
+      <c r="N106" s="167"/>
       <c r="O106" s="117" t="s">
         <v>314</v>
       </c>
@@ -12438,52 +12438,52 @@
       </c>
     </row>
     <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="172" t="s">
+      <c r="A111" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B111" s="172" t="s">
+      <c r="B111" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C111" s="172" t="s">
+      <c r="C111" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D111" s="172" t="s">
+      <c r="D111" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E111" s="172" t="s">
+      <c r="E111" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F111" s="174" t="s">
+      <c r="F111" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G111" s="160"/>
       <c r="H111" s="116"/>
-      <c r="J111" s="172" t="s">
+      <c r="J111" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K111" s="172" t="s">
+      <c r="K111" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L111" s="172" t="s">
+      <c r="L111" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M111" s="172" t="s">
+      <c r="M111" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N111" s="172" t="s">
+      <c r="N111" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O111" s="174" t="s">
+      <c r="O111" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P111" s="160"/>
     </row>
     <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="164"/>
-      <c r="B112" s="164"/>
-      <c r="C112" s="164"/>
-      <c r="D112" s="164"/>
-      <c r="E112" s="164"/>
+      <c r="A112" s="167"/>
+      <c r="B112" s="167"/>
+      <c r="C112" s="167"/>
+      <c r="D112" s="167"/>
+      <c r="E112" s="167"/>
       <c r="F112" s="117" t="s">
         <v>314</v>
       </c>
@@ -12491,11 +12491,11 @@
         <v>315</v>
       </c>
       <c r="H112" s="116"/>
-      <c r="J112" s="164"/>
-      <c r="K112" s="164"/>
-      <c r="L112" s="164"/>
-      <c r="M112" s="164"/>
-      <c r="N112" s="164"/>
+      <c r="J112" s="167"/>
+      <c r="K112" s="167"/>
+      <c r="L112" s="167"/>
+      <c r="M112" s="167"/>
+      <c r="N112" s="167"/>
       <c r="O112" s="117" t="s">
         <v>314</v>
       </c>
@@ -12571,52 +12571,52 @@
       </c>
     </row>
     <row r="117" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="172" t="s">
+      <c r="A117" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B117" s="172" t="s">
+      <c r="B117" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C117" s="172" t="s">
+      <c r="C117" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D117" s="172" t="s">
+      <c r="D117" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E117" s="172" t="s">
+      <c r="E117" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F117" s="174" t="s">
+      <c r="F117" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G117" s="160"/>
       <c r="H117" s="116"/>
-      <c r="J117" s="172" t="s">
+      <c r="J117" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K117" s="172" t="s">
+      <c r="K117" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L117" s="172" t="s">
+      <c r="L117" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M117" s="172" t="s">
+      <c r="M117" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N117" s="172" t="s">
+      <c r="N117" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O117" s="174" t="s">
+      <c r="O117" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P117" s="160"/>
     </row>
     <row r="118" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="164"/>
-      <c r="B118" s="164"/>
-      <c r="C118" s="164"/>
-      <c r="D118" s="164"/>
-      <c r="E118" s="164"/>
+      <c r="A118" s="167"/>
+      <c r="B118" s="167"/>
+      <c r="C118" s="167"/>
+      <c r="D118" s="167"/>
+      <c r="E118" s="167"/>
       <c r="F118" s="117" t="s">
         <v>314</v>
       </c>
@@ -12624,11 +12624,11 @@
         <v>315</v>
       </c>
       <c r="H118" s="116"/>
-      <c r="J118" s="164"/>
-      <c r="K118" s="164"/>
-      <c r="L118" s="164"/>
-      <c r="M118" s="164"/>
-      <c r="N118" s="164"/>
+      <c r="J118" s="167"/>
+      <c r="K118" s="167"/>
+      <c r="L118" s="167"/>
+      <c r="M118" s="167"/>
+      <c r="N118" s="167"/>
       <c r="O118" s="117" t="s">
         <v>314</v>
       </c>
@@ -12702,52 +12702,52 @@
       </c>
     </row>
     <row r="123" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="172" t="s">
+      <c r="A123" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B123" s="172" t="s">
+      <c r="B123" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C123" s="172" t="s">
+      <c r="C123" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D123" s="172" t="s">
+      <c r="D123" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E123" s="172" t="s">
+      <c r="E123" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F123" s="174" t="s">
+      <c r="F123" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G123" s="160"/>
       <c r="H123" s="116"/>
-      <c r="J123" s="172" t="s">
+      <c r="J123" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K123" s="172" t="s">
+      <c r="K123" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L123" s="172" t="s">
+      <c r="L123" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M123" s="172" t="s">
+      <c r="M123" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N123" s="172" t="s">
+      <c r="N123" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O123" s="174" t="s">
+      <c r="O123" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P123" s="160"/>
     </row>
     <row r="124" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="164"/>
-      <c r="B124" s="164"/>
-      <c r="C124" s="164"/>
-      <c r="D124" s="164"/>
-      <c r="E124" s="164"/>
+      <c r="A124" s="167"/>
+      <c r="B124" s="167"/>
+      <c r="C124" s="167"/>
+      <c r="D124" s="167"/>
+      <c r="E124" s="167"/>
       <c r="F124" s="117" t="s">
         <v>314</v>
       </c>
@@ -12755,11 +12755,11 @@
         <v>315</v>
       </c>
       <c r="H124" s="116"/>
-      <c r="J124" s="164"/>
-      <c r="K124" s="164"/>
-      <c r="L124" s="164"/>
-      <c r="M124" s="164"/>
-      <c r="N124" s="164"/>
+      <c r="J124" s="167"/>
+      <c r="K124" s="167"/>
+      <c r="L124" s="167"/>
+      <c r="M124" s="167"/>
+      <c r="N124" s="167"/>
       <c r="O124" s="117" t="s">
         <v>314</v>
       </c>
@@ -12836,52 +12836,52 @@
       </c>
     </row>
     <row r="129" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="172" t="s">
+      <c r="A129" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B129" s="172" t="s">
+      <c r="B129" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C129" s="172" t="s">
+      <c r="C129" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D129" s="172" t="s">
+      <c r="D129" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E129" s="172" t="s">
+      <c r="E129" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F129" s="174" t="s">
+      <c r="F129" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G129" s="160"/>
       <c r="H129" s="116"/>
-      <c r="J129" s="172" t="s">
+      <c r="J129" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K129" s="172" t="s">
+      <c r="K129" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L129" s="172" t="s">
+      <c r="L129" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M129" s="172" t="s">
+      <c r="M129" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N129" s="172" t="s">
+      <c r="N129" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O129" s="174" t="s">
+      <c r="O129" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P129" s="160"/>
     </row>
     <row r="130" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="164"/>
-      <c r="B130" s="164"/>
-      <c r="C130" s="164"/>
-      <c r="D130" s="164"/>
-      <c r="E130" s="164"/>
+      <c r="A130" s="167"/>
+      <c r="B130" s="167"/>
+      <c r="C130" s="167"/>
+      <c r="D130" s="167"/>
+      <c r="E130" s="167"/>
       <c r="F130" s="117" t="s">
         <v>314</v>
       </c>
@@ -12889,11 +12889,11 @@
         <v>315</v>
       </c>
       <c r="H130" s="116"/>
-      <c r="J130" s="164"/>
-      <c r="K130" s="164"/>
-      <c r="L130" s="164"/>
-      <c r="M130" s="164"/>
-      <c r="N130" s="164"/>
+      <c r="J130" s="167"/>
+      <c r="K130" s="167"/>
+      <c r="L130" s="167"/>
+      <c r="M130" s="167"/>
+      <c r="N130" s="167"/>
       <c r="O130" s="117" t="s">
         <v>314</v>
       </c>
@@ -12970,52 +12970,52 @@
       </c>
     </row>
     <row r="135" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="172" t="s">
+      <c r="A135" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B135" s="172" t="s">
+      <c r="B135" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C135" s="172" t="s">
+      <c r="C135" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D135" s="172" t="s">
+      <c r="D135" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E135" s="172" t="s">
+      <c r="E135" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F135" s="174" t="s">
+      <c r="F135" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G135" s="160"/>
       <c r="H135" s="116"/>
-      <c r="J135" s="172" t="s">
+      <c r="J135" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K135" s="172" t="s">
+      <c r="K135" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L135" s="172" t="s">
+      <c r="L135" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M135" s="172" t="s">
+      <c r="M135" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N135" s="172" t="s">
+      <c r="N135" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O135" s="174" t="s">
+      <c r="O135" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P135" s="160"/>
     </row>
     <row r="136" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="164"/>
-      <c r="B136" s="164"/>
-      <c r="C136" s="164"/>
-      <c r="D136" s="164"/>
-      <c r="E136" s="164"/>
+      <c r="A136" s="167"/>
+      <c r="B136" s="167"/>
+      <c r="C136" s="167"/>
+      <c r="D136" s="167"/>
+      <c r="E136" s="167"/>
       <c r="F136" s="117" t="s">
         <v>314</v>
       </c>
@@ -13023,11 +13023,11 @@
         <v>315</v>
       </c>
       <c r="H136" s="116"/>
-      <c r="J136" s="164"/>
-      <c r="K136" s="164"/>
-      <c r="L136" s="164"/>
-      <c r="M136" s="164"/>
-      <c r="N136" s="164"/>
+      <c r="J136" s="167"/>
+      <c r="K136" s="167"/>
+      <c r="L136" s="167"/>
+      <c r="M136" s="167"/>
+      <c r="N136" s="167"/>
       <c r="O136" s="117" t="s">
         <v>314</v>
       </c>
@@ -13971,6 +13971,222 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="228">
+    <mergeCell ref="K123:K124"/>
+    <mergeCell ref="L123:L124"/>
+    <mergeCell ref="M123:M124"/>
+    <mergeCell ref="N123:N124"/>
+    <mergeCell ref="O123:P123"/>
+    <mergeCell ref="A123:A124"/>
+    <mergeCell ref="B123:B124"/>
+    <mergeCell ref="C123:C124"/>
+    <mergeCell ref="D123:D124"/>
+    <mergeCell ref="E123:E124"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="J123:J124"/>
+    <mergeCell ref="K117:K118"/>
+    <mergeCell ref="L117:L118"/>
+    <mergeCell ref="M117:M118"/>
+    <mergeCell ref="N117:N118"/>
+    <mergeCell ref="O117:P117"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="D117:D118"/>
+    <mergeCell ref="E117:E118"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="J117:J118"/>
+    <mergeCell ref="K111:K112"/>
+    <mergeCell ref="L111:L112"/>
+    <mergeCell ref="M111:M112"/>
+    <mergeCell ref="N111:N112"/>
+    <mergeCell ref="O111:P111"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:D112"/>
+    <mergeCell ref="E111:E112"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="J111:J112"/>
+    <mergeCell ref="K105:K106"/>
+    <mergeCell ref="L105:L106"/>
+    <mergeCell ref="M105:M106"/>
+    <mergeCell ref="N105:N106"/>
+    <mergeCell ref="O105:P105"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="D105:D106"/>
+    <mergeCell ref="E105:E106"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="J105:J106"/>
+    <mergeCell ref="K96:K97"/>
+    <mergeCell ref="L96:L97"/>
+    <mergeCell ref="M96:M97"/>
+    <mergeCell ref="N96:N97"/>
+    <mergeCell ref="O96:P96"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="J96:J97"/>
+    <mergeCell ref="K90:K91"/>
+    <mergeCell ref="L90:L91"/>
+    <mergeCell ref="M90:M91"/>
+    <mergeCell ref="N90:N91"/>
+    <mergeCell ref="O90:P90"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="J90:J91"/>
+    <mergeCell ref="K81:K82"/>
+    <mergeCell ref="L81:L82"/>
+    <mergeCell ref="M81:M82"/>
+    <mergeCell ref="N81:N82"/>
+    <mergeCell ref="O81:P81"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="J81:J82"/>
+    <mergeCell ref="K135:K136"/>
+    <mergeCell ref="L135:L136"/>
+    <mergeCell ref="M135:M136"/>
+    <mergeCell ref="N135:N136"/>
+    <mergeCell ref="O135:P135"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="B135:B136"/>
+    <mergeCell ref="C135:C136"/>
+    <mergeCell ref="D135:D136"/>
+    <mergeCell ref="E135:E136"/>
+    <mergeCell ref="F135:G135"/>
+    <mergeCell ref="J135:J136"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K129:K130"/>
+    <mergeCell ref="L129:L130"/>
+    <mergeCell ref="M129:M130"/>
+    <mergeCell ref="N129:N130"/>
+    <mergeCell ref="O129:P129"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="C129:C130"/>
+    <mergeCell ref="D129:D130"/>
+    <mergeCell ref="E129:E130"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="J129:J130"/>
+    <mergeCell ref="K75:K76"/>
+    <mergeCell ref="L75:L76"/>
+    <mergeCell ref="M75:M76"/>
+    <mergeCell ref="N75:N76"/>
+    <mergeCell ref="O75:P75"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="J75:J76"/>
+    <mergeCell ref="K69:K70"/>
+    <mergeCell ref="L69:L70"/>
+    <mergeCell ref="M69:M70"/>
+    <mergeCell ref="N69:N70"/>
+    <mergeCell ref="O69:P69"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="K59:K60"/>
+    <mergeCell ref="L59:L60"/>
+    <mergeCell ref="M59:M60"/>
+    <mergeCell ref="N59:N60"/>
+    <mergeCell ref="O59:P59"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="J59:J60"/>
+    <mergeCell ref="K53:K54"/>
+    <mergeCell ref="L53:L54"/>
+    <mergeCell ref="M53:M54"/>
+    <mergeCell ref="N53:N54"/>
+    <mergeCell ref="O53:P53"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="J53:J54"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="L41:L42"/>
+    <mergeCell ref="M41:M42"/>
+    <mergeCell ref="N41:N42"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="J41:J42"/>
     <mergeCell ref="K35:K36"/>
     <mergeCell ref="L35:L36"/>
     <mergeCell ref="M35:M36"/>
@@ -13983,222 +14199,6 @@
     <mergeCell ref="E35:E36"/>
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="J35:J36"/>
-    <mergeCell ref="K41:K42"/>
-    <mergeCell ref="L41:L42"/>
-    <mergeCell ref="M41:M42"/>
-    <mergeCell ref="N41:N42"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P47"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K53:K54"/>
-    <mergeCell ref="L53:L54"/>
-    <mergeCell ref="M53:M54"/>
-    <mergeCell ref="N53:N54"/>
-    <mergeCell ref="O53:P53"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="J53:J54"/>
-    <mergeCell ref="K59:K60"/>
-    <mergeCell ref="L59:L60"/>
-    <mergeCell ref="M59:M60"/>
-    <mergeCell ref="N59:N60"/>
-    <mergeCell ref="O59:P59"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="J59:J60"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="L69:L70"/>
-    <mergeCell ref="M69:M70"/>
-    <mergeCell ref="N69:N70"/>
-    <mergeCell ref="O69:P69"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="K75:K76"/>
-    <mergeCell ref="L75:L76"/>
-    <mergeCell ref="M75:M76"/>
-    <mergeCell ref="N75:N76"/>
-    <mergeCell ref="O75:P75"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="E75:E76"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="J75:J76"/>
-    <mergeCell ref="K129:K130"/>
-    <mergeCell ref="L129:L130"/>
-    <mergeCell ref="M129:M130"/>
-    <mergeCell ref="N129:N130"/>
-    <mergeCell ref="O129:P129"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B129:B130"/>
-    <mergeCell ref="C129:C130"/>
-    <mergeCell ref="D129:D130"/>
-    <mergeCell ref="E129:E130"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="J129:J130"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="L29:L30"/>
-    <mergeCell ref="M29:M30"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K135:K136"/>
-    <mergeCell ref="L135:L136"/>
-    <mergeCell ref="M135:M136"/>
-    <mergeCell ref="N135:N136"/>
-    <mergeCell ref="O135:P135"/>
-    <mergeCell ref="A135:A136"/>
-    <mergeCell ref="B135:B136"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="D135:D136"/>
-    <mergeCell ref="E135:E136"/>
-    <mergeCell ref="F135:G135"/>
-    <mergeCell ref="J135:J136"/>
-    <mergeCell ref="K81:K82"/>
-    <mergeCell ref="L81:L82"/>
-    <mergeCell ref="M81:M82"/>
-    <mergeCell ref="N81:N82"/>
-    <mergeCell ref="O81:P81"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="J81:J82"/>
-    <mergeCell ref="K90:K91"/>
-    <mergeCell ref="L90:L91"/>
-    <mergeCell ref="M90:M91"/>
-    <mergeCell ref="N90:N91"/>
-    <mergeCell ref="O90:P90"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="J90:J91"/>
-    <mergeCell ref="K96:K97"/>
-    <mergeCell ref="L96:L97"/>
-    <mergeCell ref="M96:M97"/>
-    <mergeCell ref="N96:N97"/>
-    <mergeCell ref="O96:P96"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="J96:J97"/>
-    <mergeCell ref="K105:K106"/>
-    <mergeCell ref="L105:L106"/>
-    <mergeCell ref="M105:M106"/>
-    <mergeCell ref="N105:N106"/>
-    <mergeCell ref="O105:P105"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="D105:D106"/>
-    <mergeCell ref="E105:E106"/>
-    <mergeCell ref="F105:G105"/>
-    <mergeCell ref="J105:J106"/>
-    <mergeCell ref="K111:K112"/>
-    <mergeCell ref="L111:L112"/>
-    <mergeCell ref="M111:M112"/>
-    <mergeCell ref="N111:N112"/>
-    <mergeCell ref="O111:P111"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="D111:D112"/>
-    <mergeCell ref="E111:E112"/>
-    <mergeCell ref="F111:G111"/>
-    <mergeCell ref="J111:J112"/>
-    <mergeCell ref="K117:K118"/>
-    <mergeCell ref="L117:L118"/>
-    <mergeCell ref="M117:M118"/>
-    <mergeCell ref="N117:N118"/>
-    <mergeCell ref="O117:P117"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="C117:C118"/>
-    <mergeCell ref="D117:D118"/>
-    <mergeCell ref="E117:E118"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="J117:J118"/>
-    <mergeCell ref="K123:K124"/>
-    <mergeCell ref="L123:L124"/>
-    <mergeCell ref="M123:M124"/>
-    <mergeCell ref="N123:N124"/>
-    <mergeCell ref="O123:P123"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="D123:D124"/>
-    <mergeCell ref="E123:E124"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="J123:J124"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -14229,20 +14229,20 @@
       <c r="D1" s="178"/>
     </row>
     <row r="2" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="172" t="s">
+      <c r="A2" s="173" t="s">
         <v>160</v>
       </c>
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>330</v>
       </c>
-      <c r="C2" s="174" t="s">
+      <c r="C2" s="172" t="s">
         <v>316</v>
       </c>
       <c r="D2" s="160"/>
     </row>
     <row r="3" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="164"/>
-      <c r="B3" s="164"/>
+      <c r="A3" s="167"/>
+      <c r="B3" s="167"/>
       <c r="C3" s="79" t="s">
         <v>6</v>
       </c>
@@ -17425,52 +17425,52 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="172" t="s">
+      <c r="A5" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B5" s="172" t="s">
+      <c r="B5" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C5" s="172" t="s">
+      <c r="C5" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D5" s="172" t="s">
+      <c r="D5" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E5" s="172" t="s">
+      <c r="E5" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F5" s="174" t="s">
+      <c r="F5" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G5" s="160"/>
       <c r="H5" s="116"/>
-      <c r="J5" s="172" t="s">
+      <c r="J5" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K5" s="172" t="s">
+      <c r="K5" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L5" s="172" t="s">
+      <c r="L5" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M5" s="172" t="s">
+      <c r="M5" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N5" s="172" t="s">
+      <c r="N5" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O5" s="174" t="s">
+      <c r="O5" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P5" s="160"/>
     </row>
     <row r="6" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="164"/>
-      <c r="B6" s="164"/>
-      <c r="C6" s="164"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="164"/>
+      <c r="A6" s="167"/>
+      <c r="B6" s="167"/>
+      <c r="C6" s="167"/>
+      <c r="D6" s="167"/>
+      <c r="E6" s="167"/>
       <c r="F6" s="117" t="s">
         <v>314</v>
       </c>
@@ -17478,11 +17478,11 @@
         <v>315</v>
       </c>
       <c r="H6" s="116"/>
-      <c r="J6" s="164"/>
-      <c r="K6" s="164"/>
-      <c r="L6" s="164"/>
-      <c r="M6" s="164"/>
-      <c r="N6" s="164"/>
+      <c r="J6" s="167"/>
+      <c r="K6" s="167"/>
+      <c r="L6" s="167"/>
+      <c r="M6" s="167"/>
+      <c r="N6" s="167"/>
       <c r="O6" s="117" t="s">
         <v>314</v>
       </c>
@@ -17775,52 +17775,52 @@
       </c>
     </row>
     <row r="19" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="172" t="s">
+      <c r="A19" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B19" s="172" t="s">
+      <c r="B19" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C19" s="172" t="s">
+      <c r="C19" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D19" s="172" t="s">
+      <c r="D19" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E19" s="172" t="s">
+      <c r="E19" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F19" s="174" t="s">
+      <c r="F19" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G19" s="160"/>
       <c r="H19" s="116"/>
-      <c r="J19" s="172" t="s">
+      <c r="J19" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K19" s="172" t="s">
+      <c r="K19" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L19" s="172" t="s">
+      <c r="L19" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M19" s="172" t="s">
+      <c r="M19" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N19" s="172" t="s">
+      <c r="N19" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O19" s="174" t="s">
+      <c r="O19" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P19" s="160"/>
     </row>
     <row r="20" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="164"/>
-      <c r="B20" s="164"/>
-      <c r="C20" s="164"/>
-      <c r="D20" s="164"/>
-      <c r="E20" s="164"/>
+      <c r="A20" s="167"/>
+      <c r="B20" s="167"/>
+      <c r="C20" s="167"/>
+      <c r="D20" s="167"/>
+      <c r="E20" s="167"/>
       <c r="F20" s="117" t="s">
         <v>314</v>
       </c>
@@ -17828,11 +17828,11 @@
         <v>315</v>
       </c>
       <c r="H20" s="116"/>
-      <c r="J20" s="164"/>
-      <c r="K20" s="164"/>
-      <c r="L20" s="164"/>
-      <c r="M20" s="164"/>
-      <c r="N20" s="164"/>
+      <c r="J20" s="167"/>
+      <c r="K20" s="167"/>
+      <c r="L20" s="167"/>
+      <c r="M20" s="167"/>
+      <c r="N20" s="167"/>
       <c r="O20" s="117" t="s">
         <v>314</v>
       </c>
@@ -18025,52 +18025,52 @@
       </c>
     </row>
     <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="172" t="s">
+      <c r="A29" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B29" s="172" t="s">
+      <c r="B29" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C29" s="172" t="s">
+      <c r="C29" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D29" s="172" t="s">
+      <c r="D29" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E29" s="172" t="s">
+      <c r="E29" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F29" s="174" t="s">
+      <c r="F29" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G29" s="160"/>
       <c r="H29" s="116"/>
-      <c r="J29" s="172" t="s">
+      <c r="J29" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K29" s="172" t="s">
+      <c r="K29" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L29" s="172" t="s">
+      <c r="L29" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M29" s="172" t="s">
+      <c r="M29" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N29" s="172" t="s">
+      <c r="N29" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O29" s="174" t="s">
+      <c r="O29" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P29" s="160"/>
     </row>
     <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="164"/>
-      <c r="B30" s="164"/>
-      <c r="C30" s="164"/>
-      <c r="D30" s="164"/>
-      <c r="E30" s="164"/>
+      <c r="A30" s="167"/>
+      <c r="B30" s="167"/>
+      <c r="C30" s="167"/>
+      <c r="D30" s="167"/>
+      <c r="E30" s="167"/>
       <c r="F30" s="117" t="s">
         <v>314</v>
       </c>
@@ -18078,11 +18078,11 @@
         <v>315</v>
       </c>
       <c r="H30" s="116"/>
-      <c r="J30" s="164"/>
-      <c r="K30" s="164"/>
-      <c r="L30" s="164"/>
-      <c r="M30" s="164"/>
-      <c r="N30" s="164"/>
+      <c r="J30" s="167"/>
+      <c r="K30" s="167"/>
+      <c r="L30" s="167"/>
+      <c r="M30" s="167"/>
+      <c r="N30" s="167"/>
       <c r="O30" s="117" t="s">
         <v>314</v>
       </c>
@@ -18161,52 +18161,52 @@
       </c>
     </row>
     <row r="35" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="172" t="s">
+      <c r="A35" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B35" s="172" t="s">
+      <c r="B35" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C35" s="172" t="s">
+      <c r="C35" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D35" s="172" t="s">
+      <c r="D35" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E35" s="172" t="s">
+      <c r="E35" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F35" s="174" t="s">
+      <c r="F35" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G35" s="160"/>
       <c r="H35" s="116"/>
-      <c r="J35" s="172" t="s">
+      <c r="J35" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K35" s="172" t="s">
+      <c r="K35" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L35" s="172" t="s">
+      <c r="L35" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M35" s="172" t="s">
+      <c r="M35" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N35" s="172" t="s">
+      <c r="N35" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O35" s="174" t="s">
+      <c r="O35" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P35" s="160"/>
     </row>
     <row r="36" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="164"/>
-      <c r="B36" s="164"/>
-      <c r="C36" s="164"/>
-      <c r="D36" s="164"/>
-      <c r="E36" s="164"/>
+      <c r="A36" s="167"/>
+      <c r="B36" s="167"/>
+      <c r="C36" s="167"/>
+      <c r="D36" s="167"/>
+      <c r="E36" s="167"/>
       <c r="F36" s="117" t="s">
         <v>314</v>
       </c>
@@ -18214,11 +18214,11 @@
         <v>315</v>
       </c>
       <c r="H36" s="116"/>
-      <c r="J36" s="164"/>
-      <c r="K36" s="164"/>
-      <c r="L36" s="164"/>
-      <c r="M36" s="164"/>
-      <c r="N36" s="164"/>
+      <c r="J36" s="167"/>
+      <c r="K36" s="167"/>
+      <c r="L36" s="167"/>
+      <c r="M36" s="167"/>
+      <c r="N36" s="167"/>
       <c r="O36" s="117" t="s">
         <v>314</v>
       </c>
@@ -18297,52 +18297,52 @@
       </c>
     </row>
     <row r="41" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="172" t="s">
+      <c r="A41" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B41" s="172" t="s">
+      <c r="B41" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C41" s="172" t="s">
+      <c r="C41" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D41" s="172" t="s">
+      <c r="D41" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E41" s="172" t="s">
+      <c r="E41" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F41" s="174" t="s">
+      <c r="F41" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G41" s="160"/>
       <c r="H41" s="116"/>
-      <c r="J41" s="172" t="s">
+      <c r="J41" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K41" s="172" t="s">
+      <c r="K41" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L41" s="172" t="s">
+      <c r="L41" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M41" s="172" t="s">
+      <c r="M41" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N41" s="172" t="s">
+      <c r="N41" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O41" s="174" t="s">
+      <c r="O41" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P41" s="160"/>
     </row>
     <row r="42" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="164"/>
-      <c r="B42" s="164"/>
-      <c r="C42" s="164"/>
-      <c r="D42" s="164"/>
-      <c r="E42" s="164"/>
+      <c r="A42" s="167"/>
+      <c r="B42" s="167"/>
+      <c r="C42" s="167"/>
+      <c r="D42" s="167"/>
+      <c r="E42" s="167"/>
       <c r="F42" s="117" t="s">
         <v>314</v>
       </c>
@@ -18350,11 +18350,11 @@
         <v>315</v>
       </c>
       <c r="H42" s="116"/>
-      <c r="J42" s="164"/>
-      <c r="K42" s="164"/>
-      <c r="L42" s="164"/>
-      <c r="M42" s="164"/>
-      <c r="N42" s="164"/>
+      <c r="J42" s="167"/>
+      <c r="K42" s="167"/>
+      <c r="L42" s="167"/>
+      <c r="M42" s="167"/>
+      <c r="N42" s="167"/>
       <c r="O42" s="117" t="s">
         <v>314</v>
       </c>
@@ -18433,52 +18433,52 @@
       </c>
     </row>
     <row r="47" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="172" t="s">
+      <c r="A47" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B47" s="172" t="s">
+      <c r="B47" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C47" s="172" t="s">
+      <c r="C47" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D47" s="172" t="s">
+      <c r="D47" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E47" s="172" t="s">
+      <c r="E47" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F47" s="174" t="s">
+      <c r="F47" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G47" s="160"/>
       <c r="H47" s="116"/>
-      <c r="J47" s="172" t="s">
+      <c r="J47" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K47" s="172" t="s">
+      <c r="K47" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L47" s="172" t="s">
+      <c r="L47" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M47" s="172" t="s">
+      <c r="M47" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N47" s="172" t="s">
+      <c r="N47" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O47" s="174" t="s">
+      <c r="O47" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P47" s="160"/>
     </row>
     <row r="48" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="164"/>
-      <c r="B48" s="164"/>
-      <c r="C48" s="164"/>
-      <c r="D48" s="164"/>
-      <c r="E48" s="164"/>
+      <c r="A48" s="167"/>
+      <c r="B48" s="167"/>
+      <c r="C48" s="167"/>
+      <c r="D48" s="167"/>
+      <c r="E48" s="167"/>
       <c r="F48" s="117" t="s">
         <v>314</v>
       </c>
@@ -18486,11 +18486,11 @@
         <v>315</v>
       </c>
       <c r="H48" s="116"/>
-      <c r="J48" s="164"/>
-      <c r="K48" s="164"/>
-      <c r="L48" s="164"/>
-      <c r="M48" s="164"/>
-      <c r="N48" s="164"/>
+      <c r="J48" s="167"/>
+      <c r="K48" s="167"/>
+      <c r="L48" s="167"/>
+      <c r="M48" s="167"/>
+      <c r="N48" s="167"/>
       <c r="O48" s="117" t="s">
         <v>314</v>
       </c>
@@ -18571,52 +18571,52 @@
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="172" t="s">
+      <c r="A53" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B53" s="172" t="s">
+      <c r="B53" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C53" s="172" t="s">
+      <c r="C53" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D53" s="172" t="s">
+      <c r="D53" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E53" s="172" t="s">
+      <c r="E53" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F53" s="174" t="s">
+      <c r="F53" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G53" s="160"/>
       <c r="H53" s="116"/>
-      <c r="J53" s="172" t="s">
+      <c r="J53" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K53" s="172" t="s">
+      <c r="K53" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L53" s="172" t="s">
+      <c r="L53" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M53" s="172" t="s">
+      <c r="M53" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N53" s="172" t="s">
+      <c r="N53" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O53" s="174" t="s">
+      <c r="O53" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P53" s="160"/>
     </row>
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="164"/>
-      <c r="B54" s="164"/>
-      <c r="C54" s="164"/>
-      <c r="D54" s="164"/>
-      <c r="E54" s="164"/>
+      <c r="A54" s="167"/>
+      <c r="B54" s="167"/>
+      <c r="C54" s="167"/>
+      <c r="D54" s="167"/>
+      <c r="E54" s="167"/>
       <c r="F54" s="117" t="s">
         <v>314</v>
       </c>
@@ -18624,11 +18624,11 @@
         <v>315</v>
       </c>
       <c r="H54" s="116"/>
-      <c r="J54" s="164"/>
-      <c r="K54" s="164"/>
-      <c r="L54" s="164"/>
-      <c r="M54" s="164"/>
-      <c r="N54" s="164"/>
+      <c r="J54" s="167"/>
+      <c r="K54" s="167"/>
+      <c r="L54" s="167"/>
+      <c r="M54" s="167"/>
+      <c r="N54" s="167"/>
       <c r="O54" s="117" t="s">
         <v>314</v>
       </c>
@@ -18709,52 +18709,52 @@
       </c>
     </row>
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="172" t="s">
+      <c r="A59" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B59" s="172" t="s">
+      <c r="B59" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C59" s="172" t="s">
+      <c r="C59" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D59" s="172" t="s">
+      <c r="D59" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E59" s="172" t="s">
+      <c r="E59" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F59" s="174" t="s">
+      <c r="F59" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G59" s="160"/>
       <c r="H59" s="116"/>
-      <c r="J59" s="172" t="s">
+      <c r="J59" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K59" s="172" t="s">
+      <c r="K59" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L59" s="172" t="s">
+      <c r="L59" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M59" s="172" t="s">
+      <c r="M59" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N59" s="172" t="s">
+      <c r="N59" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O59" s="174" t="s">
+      <c r="O59" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P59" s="160"/>
     </row>
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="164"/>
-      <c r="B60" s="164"/>
-      <c r="C60" s="164"/>
-      <c r="D60" s="164"/>
-      <c r="E60" s="164"/>
+      <c r="A60" s="167"/>
+      <c r="B60" s="167"/>
+      <c r="C60" s="167"/>
+      <c r="D60" s="167"/>
+      <c r="E60" s="167"/>
       <c r="F60" s="117" t="s">
         <v>314</v>
       </c>
@@ -18762,11 +18762,11 @@
         <v>315</v>
       </c>
       <c r="H60" s="116"/>
-      <c r="J60" s="164"/>
-      <c r="K60" s="164"/>
-      <c r="L60" s="164"/>
-      <c r="M60" s="164"/>
-      <c r="N60" s="164"/>
+      <c r="J60" s="167"/>
+      <c r="K60" s="167"/>
+      <c r="L60" s="167"/>
+      <c r="M60" s="167"/>
+      <c r="N60" s="167"/>
       <c r="O60" s="117" t="s">
         <v>314</v>
       </c>
@@ -18965,52 +18965,52 @@
       </c>
     </row>
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="172" t="s">
+      <c r="A69" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B69" s="172" t="s">
+      <c r="B69" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C69" s="172" t="s">
+      <c r="C69" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D69" s="172" t="s">
+      <c r="D69" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E69" s="172" t="s">
+      <c r="E69" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F69" s="174" t="s">
+      <c r="F69" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G69" s="160"/>
       <c r="H69" s="116"/>
-      <c r="J69" s="172" t="s">
+      <c r="J69" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K69" s="172" t="s">
+      <c r="K69" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L69" s="172" t="s">
+      <c r="L69" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M69" s="172" t="s">
+      <c r="M69" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N69" s="172" t="s">
+      <c r="N69" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O69" s="174" t="s">
+      <c r="O69" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P69" s="160"/>
     </row>
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="164"/>
-      <c r="B70" s="164"/>
-      <c r="C70" s="164"/>
-      <c r="D70" s="164"/>
-      <c r="E70" s="164"/>
+      <c r="A70" s="167"/>
+      <c r="B70" s="167"/>
+      <c r="C70" s="167"/>
+      <c r="D70" s="167"/>
+      <c r="E70" s="167"/>
       <c r="F70" s="117" t="s">
         <v>314</v>
       </c>
@@ -19018,11 +19018,11 @@
         <v>315</v>
       </c>
       <c r="H70" s="116"/>
-      <c r="J70" s="164"/>
-      <c r="K70" s="164"/>
-      <c r="L70" s="164"/>
-      <c r="M70" s="164"/>
-      <c r="N70" s="164"/>
+      <c r="J70" s="167"/>
+      <c r="K70" s="167"/>
+      <c r="L70" s="167"/>
+      <c r="M70" s="167"/>
+      <c r="N70" s="167"/>
       <c r="O70" s="117" t="s">
         <v>314</v>
       </c>
@@ -19151,52 +19151,52 @@
       </c>
     </row>
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="172" t="s">
+      <c r="A76" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B76" s="172" t="s">
+      <c r="B76" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C76" s="172" t="s">
+      <c r="C76" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D76" s="172" t="s">
+      <c r="D76" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E76" s="172" t="s">
+      <c r="E76" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F76" s="174" t="s">
+      <c r="F76" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G76" s="160"/>
       <c r="H76" s="116"/>
-      <c r="J76" s="172" t="s">
+      <c r="J76" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K76" s="172" t="s">
+      <c r="K76" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L76" s="172" t="s">
+      <c r="L76" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M76" s="172" t="s">
+      <c r="M76" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N76" s="172" t="s">
+      <c r="N76" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O76" s="174" t="s">
+      <c r="O76" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P76" s="160"/>
     </row>
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="164"/>
-      <c r="B77" s="164"/>
-      <c r="C77" s="164"/>
-      <c r="D77" s="164"/>
-      <c r="E77" s="164"/>
+      <c r="A77" s="167"/>
+      <c r="B77" s="167"/>
+      <c r="C77" s="167"/>
+      <c r="D77" s="167"/>
+      <c r="E77" s="167"/>
       <c r="F77" s="117" t="s">
         <v>314</v>
       </c>
@@ -19204,11 +19204,11 @@
         <v>315</v>
       </c>
       <c r="H77" s="116"/>
-      <c r="J77" s="164"/>
-      <c r="K77" s="164"/>
-      <c r="L77" s="164"/>
-      <c r="M77" s="164"/>
-      <c r="N77" s="164"/>
+      <c r="J77" s="167"/>
+      <c r="K77" s="167"/>
+      <c r="L77" s="167"/>
+      <c r="M77" s="167"/>
+      <c r="N77" s="167"/>
       <c r="O77" s="117" t="s">
         <v>314</v>
       </c>
@@ -19307,52 +19307,52 @@
       </c>
     </row>
     <row r="82" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="172" t="s">
+      <c r="A82" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B82" s="172" t="s">
+      <c r="B82" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C82" s="172" t="s">
+      <c r="C82" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D82" s="172" t="s">
+      <c r="D82" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E82" s="172" t="s">
+      <c r="E82" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F82" s="174" t="s">
+      <c r="F82" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G82" s="160"/>
       <c r="H82" s="116"/>
-      <c r="J82" s="172" t="s">
+      <c r="J82" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K82" s="172" t="s">
+      <c r="K82" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L82" s="172" t="s">
+      <c r="L82" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M82" s="172" t="s">
+      <c r="M82" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N82" s="172" t="s">
+      <c r="N82" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O82" s="174" t="s">
+      <c r="O82" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P82" s="160"/>
     </row>
     <row r="83" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="164"/>
-      <c r="B83" s="164"/>
-      <c r="C83" s="164"/>
-      <c r="D83" s="164"/>
-      <c r="E83" s="164"/>
+      <c r="A83" s="167"/>
+      <c r="B83" s="167"/>
+      <c r="C83" s="167"/>
+      <c r="D83" s="167"/>
+      <c r="E83" s="167"/>
       <c r="F83" s="117" t="s">
         <v>314</v>
       </c>
@@ -19360,11 +19360,11 @@
         <v>315</v>
       </c>
       <c r="H83" s="116"/>
-      <c r="J83" s="164"/>
-      <c r="K83" s="164"/>
-      <c r="L83" s="164"/>
-      <c r="M83" s="164"/>
-      <c r="N83" s="164"/>
+      <c r="J83" s="167"/>
+      <c r="K83" s="167"/>
+      <c r="L83" s="167"/>
+      <c r="M83" s="167"/>
+      <c r="N83" s="167"/>
       <c r="O83" s="117" t="s">
         <v>314</v>
       </c>
@@ -19546,52 +19546,52 @@
       </c>
     </row>
     <row r="91" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="172" t="s">
+      <c r="A91" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B91" s="172" t="s">
+      <c r="B91" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C91" s="172" t="s">
+      <c r="C91" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D91" s="172" t="s">
+      <c r="D91" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E91" s="172" t="s">
+      <c r="E91" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F91" s="174" t="s">
+      <c r="F91" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G91" s="160"/>
       <c r="H91" s="116"/>
-      <c r="J91" s="172" t="s">
+      <c r="J91" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K91" s="172" t="s">
+      <c r="K91" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L91" s="172" t="s">
+      <c r="L91" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M91" s="172" t="s">
+      <c r="M91" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N91" s="172" t="s">
+      <c r="N91" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O91" s="174" t="s">
+      <c r="O91" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P91" s="160"/>
     </row>
     <row r="92" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="164"/>
-      <c r="B92" s="164"/>
-      <c r="C92" s="164"/>
-      <c r="D92" s="164"/>
-      <c r="E92" s="164"/>
+      <c r="A92" s="167"/>
+      <c r="B92" s="167"/>
+      <c r="C92" s="167"/>
+      <c r="D92" s="167"/>
+      <c r="E92" s="167"/>
       <c r="F92" s="117" t="s">
         <v>314</v>
       </c>
@@ -19599,11 +19599,11 @@
         <v>315</v>
       </c>
       <c r="H92" s="116"/>
-      <c r="J92" s="164"/>
-      <c r="K92" s="164"/>
-      <c r="L92" s="164"/>
-      <c r="M92" s="164"/>
-      <c r="N92" s="164"/>
+      <c r="J92" s="167"/>
+      <c r="K92" s="167"/>
+      <c r="L92" s="167"/>
+      <c r="M92" s="167"/>
+      <c r="N92" s="167"/>
       <c r="O92" s="117" t="s">
         <v>314</v>
       </c>
@@ -19702,52 +19702,52 @@
       </c>
     </row>
     <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="172" t="s">
+      <c r="A97" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B97" s="172" t="s">
+      <c r="B97" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C97" s="172" t="s">
+      <c r="C97" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D97" s="172" t="s">
+      <c r="D97" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E97" s="172" t="s">
+      <c r="E97" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F97" s="174" t="s">
+      <c r="F97" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G97" s="160"/>
       <c r="H97" s="116"/>
-      <c r="J97" s="172" t="s">
+      <c r="J97" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K97" s="172" t="s">
+      <c r="K97" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L97" s="172" t="s">
+      <c r="L97" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M97" s="172" t="s">
+      <c r="M97" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N97" s="172" t="s">
+      <c r="N97" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O97" s="174" t="s">
+      <c r="O97" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P97" s="160"/>
     </row>
     <row r="98" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="164"/>
-      <c r="B98" s="164"/>
-      <c r="C98" s="164"/>
-      <c r="D98" s="164"/>
-      <c r="E98" s="164"/>
+      <c r="A98" s="167"/>
+      <c r="B98" s="167"/>
+      <c r="C98" s="167"/>
+      <c r="D98" s="167"/>
+      <c r="E98" s="167"/>
       <c r="F98" s="117" t="s">
         <v>314</v>
       </c>
@@ -19755,11 +19755,11 @@
         <v>315</v>
       </c>
       <c r="H98" s="116"/>
-      <c r="J98" s="164"/>
-      <c r="K98" s="164"/>
-      <c r="L98" s="164"/>
-      <c r="M98" s="164"/>
-      <c r="N98" s="164"/>
+      <c r="J98" s="167"/>
+      <c r="K98" s="167"/>
+      <c r="L98" s="167"/>
+      <c r="M98" s="167"/>
+      <c r="N98" s="167"/>
       <c r="O98" s="117" t="s">
         <v>314</v>
       </c>
@@ -19941,52 +19941,52 @@
       </c>
     </row>
     <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="172" t="s">
+      <c r="A106" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B106" s="172" t="s">
+      <c r="B106" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C106" s="172" t="s">
+      <c r="C106" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D106" s="172" t="s">
+      <c r="D106" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E106" s="172" t="s">
+      <c r="E106" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F106" s="174" t="s">
+      <c r="F106" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G106" s="160"/>
       <c r="H106" s="116"/>
-      <c r="J106" s="172" t="s">
+      <c r="J106" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K106" s="172" t="s">
+      <c r="K106" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L106" s="172" t="s">
+      <c r="L106" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M106" s="172" t="s">
+      <c r="M106" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N106" s="172" t="s">
+      <c r="N106" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O106" s="174" t="s">
+      <c r="O106" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P106" s="160"/>
     </row>
     <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="164"/>
-      <c r="B107" s="164"/>
-      <c r="C107" s="164"/>
-      <c r="D107" s="164"/>
-      <c r="E107" s="164"/>
+      <c r="A107" s="167"/>
+      <c r="B107" s="167"/>
+      <c r="C107" s="167"/>
+      <c r="D107" s="167"/>
+      <c r="E107" s="167"/>
       <c r="F107" s="117" t="s">
         <v>314</v>
       </c>
@@ -19994,11 +19994,11 @@
         <v>315</v>
       </c>
       <c r="H107" s="116"/>
-      <c r="J107" s="164"/>
-      <c r="K107" s="164"/>
-      <c r="L107" s="164"/>
-      <c r="M107" s="164"/>
-      <c r="N107" s="164"/>
+      <c r="J107" s="167"/>
+      <c r="K107" s="167"/>
+      <c r="L107" s="167"/>
+      <c r="M107" s="167"/>
+      <c r="N107" s="167"/>
       <c r="O107" s="117" t="s">
         <v>314</v>
       </c>
@@ -20098,52 +20098,52 @@
       </c>
     </row>
     <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="172" t="s">
+      <c r="A112" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B112" s="172" t="s">
+      <c r="B112" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C112" s="172" t="s">
+      <c r="C112" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D112" s="172" t="s">
+      <c r="D112" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E112" s="172" t="s">
+      <c r="E112" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F112" s="174" t="s">
+      <c r="F112" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G112" s="160"/>
       <c r="H112" s="116"/>
-      <c r="J112" s="172" t="s">
+      <c r="J112" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K112" s="172" t="s">
+      <c r="K112" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L112" s="172" t="s">
+      <c r="L112" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M112" s="172" t="s">
+      <c r="M112" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N112" s="172" t="s">
+      <c r="N112" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O112" s="174" t="s">
+      <c r="O112" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P112" s="160"/>
     </row>
     <row r="113" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="164"/>
-      <c r="B113" s="164"/>
-      <c r="C113" s="164"/>
-      <c r="D113" s="164"/>
-      <c r="E113" s="164"/>
+      <c r="A113" s="167"/>
+      <c r="B113" s="167"/>
+      <c r="C113" s="167"/>
+      <c r="D113" s="167"/>
+      <c r="E113" s="167"/>
       <c r="F113" s="117" t="s">
         <v>314</v>
       </c>
@@ -20151,11 +20151,11 @@
         <v>315</v>
       </c>
       <c r="H113" s="116"/>
-      <c r="J113" s="164"/>
-      <c r="K113" s="164"/>
-      <c r="L113" s="164"/>
-      <c r="M113" s="164"/>
-      <c r="N113" s="164"/>
+      <c r="J113" s="167"/>
+      <c r="K113" s="167"/>
+      <c r="L113" s="167"/>
+      <c r="M113" s="167"/>
+      <c r="N113" s="167"/>
       <c r="O113" s="117" t="s">
         <v>314</v>
       </c>
@@ -20251,52 +20251,52 @@
       </c>
     </row>
     <row r="118" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="172" t="s">
+      <c r="A118" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B118" s="172" t="s">
+      <c r="B118" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C118" s="172" t="s">
+      <c r="C118" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D118" s="172" t="s">
+      <c r="D118" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E118" s="172" t="s">
+      <c r="E118" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F118" s="174" t="s">
+      <c r="F118" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G118" s="160"/>
       <c r="H118" s="116"/>
-      <c r="J118" s="172" t="s">
+      <c r="J118" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K118" s="172" t="s">
+      <c r="K118" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L118" s="172" t="s">
+      <c r="L118" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M118" s="172" t="s">
+      <c r="M118" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N118" s="172" t="s">
+      <c r="N118" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O118" s="174" t="s">
+      <c r="O118" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P118" s="160"/>
     </row>
     <row r="119" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="164"/>
-      <c r="B119" s="164"/>
-      <c r="C119" s="164"/>
-      <c r="D119" s="164"/>
-      <c r="E119" s="164"/>
+      <c r="A119" s="167"/>
+      <c r="B119" s="167"/>
+      <c r="C119" s="167"/>
+      <c r="D119" s="167"/>
+      <c r="E119" s="167"/>
       <c r="F119" s="117" t="s">
         <v>314</v>
       </c>
@@ -20304,11 +20304,11 @@
         <v>315</v>
       </c>
       <c r="H119" s="116"/>
-      <c r="J119" s="164"/>
-      <c r="K119" s="164"/>
-      <c r="L119" s="164"/>
-      <c r="M119" s="164"/>
-      <c r="N119" s="164"/>
+      <c r="J119" s="167"/>
+      <c r="K119" s="167"/>
+      <c r="L119" s="167"/>
+      <c r="M119" s="167"/>
+      <c r="N119" s="167"/>
       <c r="O119" s="117" t="s">
         <v>314</v>
       </c>
@@ -20402,52 +20402,52 @@
       </c>
     </row>
     <row r="124" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="172" t="s">
+      <c r="A124" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B124" s="172" t="s">
+      <c r="B124" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C124" s="172" t="s">
+      <c r="C124" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D124" s="172" t="s">
+      <c r="D124" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E124" s="172" t="s">
+      <c r="E124" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F124" s="174" t="s">
+      <c r="F124" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G124" s="160"/>
       <c r="H124" s="116"/>
-      <c r="J124" s="172" t="s">
+      <c r="J124" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K124" s="172" t="s">
+      <c r="K124" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L124" s="172" t="s">
+      <c r="L124" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M124" s="172" t="s">
+      <c r="M124" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N124" s="172" t="s">
+      <c r="N124" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O124" s="174" t="s">
+      <c r="O124" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P124" s="160"/>
     </row>
     <row r="125" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="164"/>
-      <c r="B125" s="164"/>
-      <c r="C125" s="164"/>
-      <c r="D125" s="164"/>
-      <c r="E125" s="164"/>
+      <c r="A125" s="167"/>
+      <c r="B125" s="167"/>
+      <c r="C125" s="167"/>
+      <c r="D125" s="167"/>
+      <c r="E125" s="167"/>
       <c r="F125" s="117" t="s">
         <v>314</v>
       </c>
@@ -20455,11 +20455,11 @@
         <v>315</v>
       </c>
       <c r="H125" s="116"/>
-      <c r="J125" s="164"/>
-      <c r="K125" s="164"/>
-      <c r="L125" s="164"/>
-      <c r="M125" s="164"/>
-      <c r="N125" s="164"/>
+      <c r="J125" s="167"/>
+      <c r="K125" s="167"/>
+      <c r="L125" s="167"/>
+      <c r="M125" s="167"/>
+      <c r="N125" s="167"/>
       <c r="O125" s="117" t="s">
         <v>314</v>
       </c>
@@ -20556,52 +20556,52 @@
       </c>
     </row>
     <row r="130" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="172" t="s">
+      <c r="A130" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B130" s="172" t="s">
+      <c r="B130" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C130" s="172" t="s">
+      <c r="C130" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D130" s="172" t="s">
+      <c r="D130" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E130" s="172" t="s">
+      <c r="E130" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F130" s="174" t="s">
+      <c r="F130" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G130" s="160"/>
       <c r="H130" s="116"/>
-      <c r="J130" s="172" t="s">
+      <c r="J130" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K130" s="172" t="s">
+      <c r="K130" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L130" s="172" t="s">
+      <c r="L130" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M130" s="172" t="s">
+      <c r="M130" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N130" s="172" t="s">
+      <c r="N130" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O130" s="174" t="s">
+      <c r="O130" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P130" s="160"/>
     </row>
     <row r="131" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="164"/>
-      <c r="B131" s="164"/>
-      <c r="C131" s="164"/>
-      <c r="D131" s="164"/>
-      <c r="E131" s="164"/>
+      <c r="A131" s="167"/>
+      <c r="B131" s="167"/>
+      <c r="C131" s="167"/>
+      <c r="D131" s="167"/>
+      <c r="E131" s="167"/>
       <c r="F131" s="117" t="s">
         <v>314</v>
       </c>
@@ -20609,11 +20609,11 @@
         <v>315</v>
       </c>
       <c r="H131" s="116"/>
-      <c r="J131" s="164"/>
-      <c r="K131" s="164"/>
-      <c r="L131" s="164"/>
-      <c r="M131" s="164"/>
-      <c r="N131" s="164"/>
+      <c r="J131" s="167"/>
+      <c r="K131" s="167"/>
+      <c r="L131" s="167"/>
+      <c r="M131" s="167"/>
+      <c r="N131" s="167"/>
       <c r="O131" s="117" t="s">
         <v>314</v>
       </c>
@@ -20710,52 +20710,52 @@
       </c>
     </row>
     <row r="136" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="172" t="s">
+      <c r="A136" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B136" s="172" t="s">
+      <c r="B136" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C136" s="172" t="s">
+      <c r="C136" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D136" s="172" t="s">
+      <c r="D136" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E136" s="172" t="s">
+      <c r="E136" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F136" s="174" t="s">
+      <c r="F136" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G136" s="160"/>
       <c r="H136" s="116"/>
-      <c r="J136" s="172" t="s">
+      <c r="J136" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K136" s="172" t="s">
+      <c r="K136" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L136" s="172" t="s">
+      <c r="L136" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M136" s="172" t="s">
+      <c r="M136" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N136" s="172" t="s">
+      <c r="N136" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O136" s="174" t="s">
+      <c r="O136" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P136" s="160"/>
     </row>
     <row r="137" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="164"/>
-      <c r="B137" s="164"/>
-      <c r="C137" s="164"/>
-      <c r="D137" s="164"/>
-      <c r="E137" s="164"/>
+      <c r="A137" s="167"/>
+      <c r="B137" s="167"/>
+      <c r="C137" s="167"/>
+      <c r="D137" s="167"/>
+      <c r="E137" s="167"/>
       <c r="F137" s="117" t="s">
         <v>314</v>
       </c>
@@ -20763,11 +20763,11 @@
         <v>315</v>
       </c>
       <c r="H137" s="116"/>
-      <c r="J137" s="164"/>
-      <c r="K137" s="164"/>
-      <c r="L137" s="164"/>
-      <c r="M137" s="164"/>
-      <c r="N137" s="164"/>
+      <c r="J137" s="167"/>
+      <c r="K137" s="167"/>
+      <c r="L137" s="167"/>
+      <c r="M137" s="167"/>
+      <c r="N137" s="167"/>
       <c r="O137" s="117" t="s">
         <v>314</v>
       </c>
@@ -20864,52 +20864,52 @@
       </c>
     </row>
     <row r="142" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="172" t="s">
+      <c r="A142" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B142" s="172" t="s">
+      <c r="B142" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C142" s="172" t="s">
+      <c r="C142" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D142" s="172" t="s">
+      <c r="D142" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E142" s="172" t="s">
+      <c r="E142" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F142" s="174" t="s">
+      <c r="F142" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G142" s="160"/>
       <c r="H142" s="116"/>
-      <c r="J142" s="172" t="s">
+      <c r="J142" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K142" s="172" t="s">
+      <c r="K142" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L142" s="172" t="s">
+      <c r="L142" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M142" s="172" t="s">
+      <c r="M142" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N142" s="172" t="s">
+      <c r="N142" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O142" s="174" t="s">
+      <c r="O142" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P142" s="160"/>
     </row>
     <row r="143" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="164"/>
-      <c r="B143" s="164"/>
-      <c r="C143" s="164"/>
-      <c r="D143" s="164"/>
-      <c r="E143" s="164"/>
+      <c r="A143" s="167"/>
+      <c r="B143" s="167"/>
+      <c r="C143" s="167"/>
+      <c r="D143" s="167"/>
+      <c r="E143" s="167"/>
       <c r="F143" s="117" t="s">
         <v>314</v>
       </c>
@@ -20917,11 +20917,11 @@
         <v>315</v>
       </c>
       <c r="H143" s="116"/>
-      <c r="J143" s="164"/>
-      <c r="K143" s="164"/>
-      <c r="L143" s="164"/>
-      <c r="M143" s="164"/>
-      <c r="N143" s="164"/>
+      <c r="J143" s="167"/>
+      <c r="K143" s="167"/>
+      <c r="L143" s="167"/>
+      <c r="M143" s="167"/>
+      <c r="N143" s="167"/>
       <c r="O143" s="117" t="s">
         <v>314</v>
       </c>
@@ -21053,52 +21053,52 @@
       </c>
     </row>
     <row r="151" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="172" t="s">
+      <c r="A151" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B151" s="172" t="s">
+      <c r="B151" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="C151" s="172" t="s">
+      <c r="C151" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="D151" s="172" t="s">
+      <c r="D151" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="E151" s="172" t="s">
+      <c r="E151" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="F151" s="174" t="s">
+      <c r="F151" s="172" t="s">
         <v>316</v>
       </c>
       <c r="G151" s="160"/>
       <c r="H151" s="137"/>
-      <c r="J151" s="172" t="s">
+      <c r="J151" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="K151" s="172" t="s">
+      <c r="K151" s="173" t="s">
         <v>229</v>
       </c>
-      <c r="L151" s="172" t="s">
+      <c r="L151" s="173" t="s">
         <v>313</v>
       </c>
-      <c r="M151" s="172" t="s">
+      <c r="M151" s="173" t="s">
         <v>314</v>
       </c>
-      <c r="N151" s="172" t="s">
+      <c r="N151" s="173" t="s">
         <v>315</v>
       </c>
-      <c r="O151" s="174" t="s">
+      <c r="O151" s="172" t="s">
         <v>316</v>
       </c>
       <c r="P151" s="160"/>
     </row>
     <row r="152" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="164"/>
-      <c r="B152" s="164"/>
-      <c r="C152" s="164"/>
-      <c r="D152" s="164"/>
-      <c r="E152" s="164"/>
+      <c r="A152" s="167"/>
+      <c r="B152" s="167"/>
+      <c r="C152" s="167"/>
+      <c r="D152" s="167"/>
+      <c r="E152" s="167"/>
       <c r="F152" s="117" t="s">
         <v>314</v>
       </c>
@@ -21106,11 +21106,11 @@
         <v>315</v>
       </c>
       <c r="H152" s="137"/>
-      <c r="J152" s="164"/>
-      <c r="K152" s="164"/>
-      <c r="L152" s="164"/>
-      <c r="M152" s="164"/>
-      <c r="N152" s="164"/>
+      <c r="J152" s="167"/>
+      <c r="K152" s="167"/>
+      <c r="L152" s="167"/>
+      <c r="M152" s="167"/>
+      <c r="N152" s="167"/>
       <c r="O152" s="117" t="s">
         <v>314</v>
       </c>
@@ -22072,6 +22072,246 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="252">
+    <mergeCell ref="K124:K125"/>
+    <mergeCell ref="L124:L125"/>
+    <mergeCell ref="M124:M125"/>
+    <mergeCell ref="N124:N125"/>
+    <mergeCell ref="O124:P124"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="J124:J125"/>
+    <mergeCell ref="K118:K119"/>
+    <mergeCell ref="L118:L119"/>
+    <mergeCell ref="M118:M119"/>
+    <mergeCell ref="N118:N119"/>
+    <mergeCell ref="O118:P118"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
+    <mergeCell ref="E118:E119"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="J118:J119"/>
+    <mergeCell ref="K112:K113"/>
+    <mergeCell ref="L112:L113"/>
+    <mergeCell ref="M112:M113"/>
+    <mergeCell ref="N112:N113"/>
+    <mergeCell ref="O112:P112"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="D112:D113"/>
+    <mergeCell ref="E112:E113"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="J112:J113"/>
+    <mergeCell ref="K106:K107"/>
+    <mergeCell ref="L106:L107"/>
+    <mergeCell ref="M106:M107"/>
+    <mergeCell ref="N106:N107"/>
+    <mergeCell ref="O106:P106"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="J106:J107"/>
+    <mergeCell ref="K97:K98"/>
+    <mergeCell ref="L97:L98"/>
+    <mergeCell ref="M97:M98"/>
+    <mergeCell ref="N97:N98"/>
+    <mergeCell ref="O97:P97"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="E97:E98"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="J97:J98"/>
+    <mergeCell ref="K91:K92"/>
+    <mergeCell ref="L91:L92"/>
+    <mergeCell ref="M91:M92"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:P91"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:D92"/>
+    <mergeCell ref="E91:E92"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="J91:J92"/>
+    <mergeCell ref="K82:K83"/>
+    <mergeCell ref="L82:L83"/>
+    <mergeCell ref="M82:M83"/>
+    <mergeCell ref="N82:N83"/>
+    <mergeCell ref="O82:P82"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="E82:E83"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="J82:J83"/>
+    <mergeCell ref="K151:K152"/>
+    <mergeCell ref="L151:L152"/>
+    <mergeCell ref="M151:M152"/>
+    <mergeCell ref="N151:N152"/>
+    <mergeCell ref="O151:P151"/>
+    <mergeCell ref="A151:A152"/>
+    <mergeCell ref="B151:B152"/>
+    <mergeCell ref="C151:C152"/>
+    <mergeCell ref="D151:D152"/>
+    <mergeCell ref="E151:E152"/>
+    <mergeCell ref="F151:G151"/>
+    <mergeCell ref="J151:J152"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K142:K143"/>
+    <mergeCell ref="L142:L143"/>
+    <mergeCell ref="M142:M143"/>
+    <mergeCell ref="N142:N143"/>
+    <mergeCell ref="O142:P142"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="E142:E143"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="J142:J143"/>
+    <mergeCell ref="K136:K137"/>
+    <mergeCell ref="L136:L137"/>
+    <mergeCell ref="M136:M137"/>
+    <mergeCell ref="N136:N137"/>
+    <mergeCell ref="O136:P136"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:G136"/>
+    <mergeCell ref="J136:J137"/>
+    <mergeCell ref="K130:K131"/>
+    <mergeCell ref="L130:L131"/>
+    <mergeCell ref="M130:M131"/>
+    <mergeCell ref="N130:N131"/>
+    <mergeCell ref="O130:P130"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
+    <mergeCell ref="E130:E131"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="J130:J131"/>
+    <mergeCell ref="K76:K77"/>
+    <mergeCell ref="L76:L77"/>
+    <mergeCell ref="M76:M77"/>
+    <mergeCell ref="N76:N77"/>
+    <mergeCell ref="O76:P76"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="J76:J77"/>
+    <mergeCell ref="K69:K70"/>
+    <mergeCell ref="L69:L70"/>
+    <mergeCell ref="M69:M70"/>
+    <mergeCell ref="N69:N70"/>
+    <mergeCell ref="O69:P69"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="K59:K60"/>
+    <mergeCell ref="L59:L60"/>
+    <mergeCell ref="M59:M60"/>
+    <mergeCell ref="N59:N60"/>
+    <mergeCell ref="O59:P59"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="J59:J60"/>
+    <mergeCell ref="K53:K54"/>
+    <mergeCell ref="L53:L54"/>
+    <mergeCell ref="M53:M54"/>
+    <mergeCell ref="N53:N54"/>
+    <mergeCell ref="O53:P53"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="J53:J54"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="L41:L42"/>
+    <mergeCell ref="M41:M42"/>
+    <mergeCell ref="N41:N42"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="J41:J42"/>
     <mergeCell ref="K35:K36"/>
     <mergeCell ref="L35:L36"/>
     <mergeCell ref="M35:M36"/>
@@ -22084,246 +22324,6 @@
     <mergeCell ref="E35:E36"/>
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="J35:J36"/>
-    <mergeCell ref="K41:K42"/>
-    <mergeCell ref="L41:L42"/>
-    <mergeCell ref="M41:M42"/>
-    <mergeCell ref="N41:N42"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P47"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K53:K54"/>
-    <mergeCell ref="L53:L54"/>
-    <mergeCell ref="M53:M54"/>
-    <mergeCell ref="N53:N54"/>
-    <mergeCell ref="O53:P53"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="J53:J54"/>
-    <mergeCell ref="K59:K60"/>
-    <mergeCell ref="L59:L60"/>
-    <mergeCell ref="M59:M60"/>
-    <mergeCell ref="N59:N60"/>
-    <mergeCell ref="O59:P59"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="J59:J60"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="L69:L70"/>
-    <mergeCell ref="M69:M70"/>
-    <mergeCell ref="N69:N70"/>
-    <mergeCell ref="O69:P69"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="K76:K77"/>
-    <mergeCell ref="L76:L77"/>
-    <mergeCell ref="M76:M77"/>
-    <mergeCell ref="N76:N77"/>
-    <mergeCell ref="O76:P76"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:C77"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="J76:J77"/>
-    <mergeCell ref="K130:K131"/>
-    <mergeCell ref="L130:L131"/>
-    <mergeCell ref="M130:M131"/>
-    <mergeCell ref="N130:N131"/>
-    <mergeCell ref="O130:P130"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="D130:D131"/>
-    <mergeCell ref="E130:E131"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="J130:J131"/>
-    <mergeCell ref="K136:K137"/>
-    <mergeCell ref="L136:L137"/>
-    <mergeCell ref="M136:M137"/>
-    <mergeCell ref="N136:N137"/>
-    <mergeCell ref="O136:P136"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:G136"/>
-    <mergeCell ref="J136:J137"/>
-    <mergeCell ref="K142:K143"/>
-    <mergeCell ref="L142:L143"/>
-    <mergeCell ref="M142:M143"/>
-    <mergeCell ref="N142:N143"/>
-    <mergeCell ref="O142:P142"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="E142:E143"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="J142:J143"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="L29:L30"/>
-    <mergeCell ref="M29:M30"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K151:K152"/>
-    <mergeCell ref="L151:L152"/>
-    <mergeCell ref="M151:M152"/>
-    <mergeCell ref="N151:N152"/>
-    <mergeCell ref="O151:P151"/>
-    <mergeCell ref="A151:A152"/>
-    <mergeCell ref="B151:B152"/>
-    <mergeCell ref="C151:C152"/>
-    <mergeCell ref="D151:D152"/>
-    <mergeCell ref="E151:E152"/>
-    <mergeCell ref="F151:G151"/>
-    <mergeCell ref="J151:J152"/>
-    <mergeCell ref="K82:K83"/>
-    <mergeCell ref="L82:L83"/>
-    <mergeCell ref="M82:M83"/>
-    <mergeCell ref="N82:N83"/>
-    <mergeCell ref="O82:P82"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="J82:J83"/>
-    <mergeCell ref="K91:K92"/>
-    <mergeCell ref="L91:L92"/>
-    <mergeCell ref="M91:M92"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:P91"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:D92"/>
-    <mergeCell ref="E91:E92"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="J91:J92"/>
-    <mergeCell ref="K97:K98"/>
-    <mergeCell ref="L97:L98"/>
-    <mergeCell ref="M97:M98"/>
-    <mergeCell ref="N97:N98"/>
-    <mergeCell ref="O97:P97"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="E97:E98"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="J97:J98"/>
-    <mergeCell ref="K106:K107"/>
-    <mergeCell ref="L106:L107"/>
-    <mergeCell ref="M106:M107"/>
-    <mergeCell ref="N106:N107"/>
-    <mergeCell ref="O106:P106"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="C106:C107"/>
-    <mergeCell ref="D106:D107"/>
-    <mergeCell ref="E106:E107"/>
-    <mergeCell ref="F106:G106"/>
-    <mergeCell ref="J106:J107"/>
-    <mergeCell ref="K112:K113"/>
-    <mergeCell ref="L112:L113"/>
-    <mergeCell ref="M112:M113"/>
-    <mergeCell ref="N112:N113"/>
-    <mergeCell ref="O112:P112"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="D112:D113"/>
-    <mergeCell ref="E112:E113"/>
-    <mergeCell ref="F112:G112"/>
-    <mergeCell ref="J112:J113"/>
-    <mergeCell ref="K118:K119"/>
-    <mergeCell ref="L118:L119"/>
-    <mergeCell ref="M118:M119"/>
-    <mergeCell ref="N118:N119"/>
-    <mergeCell ref="O118:P118"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="E118:E119"/>
-    <mergeCell ref="F118:G118"/>
-    <mergeCell ref="J118:J119"/>
-    <mergeCell ref="K124:K125"/>
-    <mergeCell ref="L124:L125"/>
-    <mergeCell ref="M124:M125"/>
-    <mergeCell ref="N124:N125"/>
-    <mergeCell ref="O124:P124"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="J124:J125"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -22364,8 +22364,8 @@
       <c r="D2" s="160"/>
     </row>
     <row r="3" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="164"/>
-      <c r="B3" s="164"/>
+      <c r="A3" s="167"/>
+      <c r="B3" s="167"/>
       <c r="C3" s="28" t="s">
         <v>6</v>
       </c>
@@ -33119,32 +33119,32 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="165" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="162" t="s">
+      <c r="B2" s="165" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="162" t="s">
+      <c r="C2" s="165" t="s">
         <v>193</v>
       </c>
-      <c r="D2" s="165" t="s">
+      <c r="D2" s="168" t="s">
         <v>194</v>
       </c>
       <c r="E2" s="159"/>
       <c r="F2" s="160"/>
-      <c r="G2" s="162" t="s">
+      <c r="G2" s="165" t="s">
         <v>195</v>
       </c>
-      <c r="H2" s="165" t="s">
+      <c r="H2" s="168" t="s">
         <v>196</v>
       </c>
       <c r="I2" s="160"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="163"/>
-      <c r="B3" s="163"/>
-      <c r="C3" s="163"/>
+      <c r="A3" s="166"/>
+      <c r="B3" s="166"/>
+      <c r="C3" s="166"/>
       <c r="D3" s="31" t="s">
         <v>9</v>
       </c>
@@ -33154,18 +33154,18 @@
       <c r="F3" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="163"/>
-      <c r="H3" s="162" t="s">
+      <c r="G3" s="166"/>
+      <c r="H3" s="165" t="s">
         <v>197</v>
       </c>
-      <c r="I3" s="162" t="s">
+      <c r="I3" s="165" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="164"/>
-      <c r="B4" s="164"/>
-      <c r="C4" s="164"/>
+      <c r="A4" s="167"/>
+      <c r="B4" s="167"/>
+      <c r="C4" s="167"/>
       <c r="D4" s="31" t="s">
         <v>199</v>
       </c>
@@ -33175,9 +33175,9 @@
       <c r="F4" s="32" t="s">
         <v>199</v>
       </c>
-      <c r="G4" s="164"/>
-      <c r="H4" s="164"/>
-      <c r="I4" s="164"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
+      <c r="I4" s="167"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
@@ -33463,11 +33463,11 @@
       <c r="I23" s="40"/>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="166" t="s">
+      <c r="A24" s="162" t="s">
         <v>188</v>
       </c>
-      <c r="B24" s="167"/>
-      <c r="C24" s="168"/>
+      <c r="B24" s="163"/>
+      <c r="C24" s="164"/>
       <c r="D24" s="41">
         <f t="shared" ref="D24:F24" si="0">SUM(D5:D23)</f>
         <v>11500000</v>
@@ -34591,16 +34591,16 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="C2:C4"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="C2:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -34629,13 +34629,13 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="165" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="162" t="s">
+      <c r="B2" s="165" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="162" t="s">
+      <c r="C2" s="165" t="s">
         <v>215</v>
       </c>
       <c r="D2" s="31" t="s">
@@ -34644,21 +34644,21 @@
       <c r="E2" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="F2" s="162" t="s">
+      <c r="F2" s="165" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="164"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="164"/>
+      <c r="A3" s="167"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="167"/>
       <c r="D3" s="31" t="s">
         <v>199</v>
       </c>
       <c r="E3" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="F3" s="164"/>
+      <c r="F3" s="167"/>
     </row>
     <row r="4" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
@@ -35950,13 +35950,13 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="165" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="162" t="s">
+      <c r="B2" s="165" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="162" t="s">
+      <c r="C2" s="165" t="s">
         <v>229</v>
       </c>
       <c r="D2" s="32" t="s">
@@ -35968,21 +35968,21 @@
       <c r="F2" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="162" t="s">
+      <c r="G2" s="165" t="s">
         <v>195</v>
       </c>
-      <c r="H2" s="165" t="s">
+      <c r="H2" s="168" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="160"/>
-      <c r="J2" s="162" t="s">
+      <c r="J2" s="165" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="164"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="164"/>
+      <c r="A3" s="167"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="167"/>
       <c r="D3" s="32" t="s">
         <v>6</v>
       </c>
@@ -35992,14 +35992,14 @@
       <c r="F3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="164"/>
+      <c r="G3" s="167"/>
       <c r="H3" s="32" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="164"/>
+      <c r="J3" s="167"/>
     </row>
     <row r="4" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="33"/>
@@ -39337,13 +39337,13 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="165" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="162" t="s">
+      <c r="B2" s="165" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="162" t="s">
+      <c r="C2" s="165" t="s">
         <v>229</v>
       </c>
       <c r="D2" s="32" t="s">
@@ -39355,21 +39355,21 @@
       <c r="F2" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="G2" s="162" t="s">
+      <c r="G2" s="165" t="s">
         <v>195</v>
       </c>
-      <c r="H2" s="165" t="s">
+      <c r="H2" s="168" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="160"/>
-      <c r="J2" s="162" t="s">
+      <c r="J2" s="165" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="164"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="164"/>
+      <c r="A3" s="167"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="167"/>
       <c r="D3" s="32" t="s">
         <v>7</v>
       </c>
@@ -39379,14 +39379,14 @@
       <c r="F3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="164"/>
+      <c r="G3" s="167"/>
       <c r="H3" s="32" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="164"/>
+      <c r="J3" s="167"/>
     </row>
     <row r="4" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="33"/>
@@ -42527,56 +42527,56 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="172" t="s">
+      <c r="A2" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="173" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="174" t="s">
+      <c r="C2" s="172" t="s">
         <v>229</v>
       </c>
       <c r="D2" s="159"/>
       <c r="E2" s="159"/>
       <c r="F2" s="160"/>
-      <c r="G2" s="172" t="s">
+      <c r="G2" s="173" t="s">
         <v>264</v>
       </c>
-      <c r="H2" s="172" t="s">
+      <c r="H2" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="172" t="s">
+      <c r="I2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="173" t="s">
+      <c r="J2" s="174" t="s">
         <v>265</v>
       </c>
-      <c r="N2" s="172" t="s">
+      <c r="N2" s="173" t="s">
         <v>266</v>
       </c>
-      <c r="O2" s="172" t="s">
+      <c r="O2" s="173" t="s">
         <v>267</v>
       </c>
-      <c r="P2" s="172" t="s">
+      <c r="P2" s="173" t="s">
         <v>189</v>
       </c>
-      <c r="Q2" s="172" t="s">
+      <c r="Q2" s="173" t="s">
         <v>58</v>
       </c>
-      <c r="R2" s="172" t="s">
+      <c r="R2" s="173" t="s">
         <v>79</v>
       </c>
-      <c r="S2" s="174" t="s">
+      <c r="S2" s="172" t="s">
         <v>268</v>
       </c>
       <c r="T2" s="160"/>
-      <c r="U2" s="172" t="s">
+      <c r="U2" s="173" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="164"/>
-      <c r="B3" s="164"/>
+      <c r="A3" s="167"/>
+      <c r="B3" s="167"/>
       <c r="C3" s="79" t="s">
         <v>270</v>
       </c>
@@ -42589,22 +42589,22 @@
       <c r="F3" s="79" t="s">
         <v>273</v>
       </c>
-      <c r="G3" s="164"/>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="164"/>
-      <c r="N3" s="164"/>
-      <c r="O3" s="164"/>
-      <c r="P3" s="164"/>
-      <c r="Q3" s="164"/>
-      <c r="R3" s="164"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="167"/>
+      <c r="I3" s="167"/>
+      <c r="J3" s="167"/>
+      <c r="N3" s="167"/>
+      <c r="O3" s="167"/>
+      <c r="P3" s="167"/>
+      <c r="Q3" s="167"/>
+      <c r="R3" s="167"/>
       <c r="S3" s="81" t="s">
         <v>6</v>
       </c>
       <c r="T3" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="U3" s="164"/>
+      <c r="U3" s="167"/>
     </row>
     <row r="4" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
@@ -42863,34 +42863,34 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="172" t="s">
+      <c r="A19" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B19" s="172" t="s">
+      <c r="B19" s="173" t="s">
         <v>192</v>
       </c>
-      <c r="C19" s="174" t="s">
+      <c r="C19" s="172" t="s">
         <v>229</v>
       </c>
       <c r="D19" s="159"/>
       <c r="E19" s="159"/>
       <c r="F19" s="160"/>
-      <c r="G19" s="172" t="s">
+      <c r="G19" s="173" t="s">
         <v>264</v>
       </c>
-      <c r="H19" s="172" t="s">
+      <c r="H19" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="I19" s="172" t="s">
+      <c r="I19" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="J19" s="173" t="s">
+      <c r="J19" s="174" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="164"/>
-      <c r="B20" s="164"/>
+      <c r="A20" s="167"/>
+      <c r="B20" s="167"/>
       <c r="C20" s="79" t="s">
         <v>270</v>
       </c>
@@ -42903,10 +42903,10 @@
       <c r="F20" s="79" t="s">
         <v>273</v>
       </c>
-      <c r="G20" s="164"/>
-      <c r="H20" s="164"/>
-      <c r="I20" s="164"/>
-      <c r="J20" s="164"/>
+      <c r="G20" s="167"/>
+      <c r="H20" s="167"/>
+      <c r="I20" s="167"/>
+      <c r="J20" s="167"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="82" t="s">
@@ -43122,34 +43122,34 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="172" t="s">
+      <c r="A36" s="173" t="s">
         <v>191</v>
       </c>
-      <c r="B36" s="172" t="s">
+      <c r="B36" s="173" t="s">
         <v>192</v>
       </c>
-      <c r="C36" s="174" t="s">
+      <c r="C36" s="172" t="s">
         <v>229</v>
       </c>
       <c r="D36" s="159"/>
       <c r="E36" s="159"/>
       <c r="F36" s="160"/>
-      <c r="G36" s="172" t="s">
+      <c r="G36" s="173" t="s">
         <v>264</v>
       </c>
-      <c r="H36" s="172" t="s">
+      <c r="H36" s="173" t="s">
         <v>6</v>
       </c>
-      <c r="I36" s="172" t="s">
+      <c r="I36" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="J36" s="173" t="s">
+      <c r="J36" s="174" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="164"/>
-      <c r="B37" s="164"/>
+      <c r="A37" s="167"/>
+      <c r="B37" s="167"/>
       <c r="C37" s="79" t="s">
         <v>270</v>
       </c>
@@ -43162,10 +43162,10 @@
       <c r="F37" s="79" t="s">
         <v>273</v>
       </c>
-      <c r="G37" s="164"/>
-      <c r="H37" s="164"/>
-      <c r="I37" s="164"/>
-      <c r="J37" s="164"/>
+      <c r="G37" s="167"/>
+      <c r="H37" s="167"/>
+      <c r="I37" s="167"/>
+      <c r="J37" s="167"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="36" t="s">
@@ -44291,6 +44291,20 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="U2:U3"/>
     <mergeCell ref="A2:A3"/>
@@ -44305,20 +44319,6 @@
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
